--- a/backend/uploads/Class_List_Only_Styled.xlsx
+++ b/backend/uploads/Class_List_Only_Styled.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ian\Desktop\SYSTEM FOR 2ND SEM\stone\backend\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendr\Desktop\stone\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FD6D11-9EB1-44A7-9466-20253CFF66A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1352EED1-D349-4739-A692-E69FF5BACAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="19200" windowHeight="10510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class List" sheetId="1" r:id="rId1"/>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Descriptive Title:</t>
-  </si>
-  <si>
-    <t>Animation Design and Production</t>
   </si>
   <si>
     <t>Semester:</t>
@@ -177,17 +174,20 @@
     <t>Valdez, John Winchel</t>
   </si>
   <si>
-    <t>DA 14123</t>
+    <t>T205</t>
   </si>
   <si>
-    <t>T397</t>
+    <t>BA 13131</t>
+  </si>
+  <si>
+    <t>Computer Programming 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +233,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -815,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -992,35 +997,48 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1032,24 +1050,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1359,31 +1367,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CX317"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="31.85546875" customWidth="1"/>
-    <col min="8" max="21" width="5.28515625" customWidth="1"/>
-    <col min="22" max="22" width="5.85546875" customWidth="1"/>
-    <col min="23" max="26" width="5.28515625" customWidth="1"/>
-    <col min="27" max="30" width="5.28515625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="6.28515625" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.28515625" hidden="1" customWidth="1"/>
-    <col min="37" max="72" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="73" max="75" width="5.5703125" customWidth="1"/>
-    <col min="76" max="91" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="92" max="92" width="0.140625" customWidth="1"/>
-    <col min="93" max="93" width="5.5703125" customWidth="1"/>
-    <col min="94" max="94" width="5.28515625" customWidth="1"/>
-    <col min="95" max="102" width="5.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="31.81640625" customWidth="1"/>
+    <col min="8" max="21" width="5.26953125" customWidth="1"/>
+    <col min="22" max="22" width="5.81640625" customWidth="1"/>
+    <col min="23" max="26" width="5.26953125" customWidth="1"/>
+    <col min="27" max="30" width="5.26953125" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="6.26953125" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.26953125" hidden="1" customWidth="1"/>
+    <col min="37" max="72" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="73" max="75" width="5.54296875" customWidth="1"/>
+    <col min="76" max="91" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="92" max="92" width="0.1796875" customWidth="1"/>
+    <col min="93" max="93" width="5.54296875" customWidth="1"/>
+    <col min="94" max="94" width="5.26953125" customWidth="1"/>
+    <col min="95" max="102" width="5.26953125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:102" x14ac:dyDescent="0.25">
+    <row r="1" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
       <c r="E1" s="1">
         <v>94</v>
       </c>
@@ -1485,313 +1493,313 @@
       <c r="CW1" s="1"/>
       <c r="CX1" s="1"/>
     </row>
-    <row r="2" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E2" s="82" t="s">
+    <row r="2" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
-      <c r="AI2" s="80"/>
-      <c r="AJ2" s="80"/>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80"/>
-      <c r="AM2" s="80"/>
-      <c r="AN2" s="80"/>
-      <c r="AO2" s="80"/>
-      <c r="AP2" s="80"/>
-      <c r="AQ2" s="80"/>
-      <c r="AR2" s="80"/>
-      <c r="AS2" s="80"/>
-      <c r="AT2" s="80"/>
-      <c r="AU2" s="80"/>
-      <c r="AV2" s="80"/>
-      <c r="AW2" s="80"/>
-      <c r="AX2" s="80"/>
-      <c r="AY2" s="80"/>
-      <c r="AZ2" s="80"/>
-      <c r="BA2" s="80"/>
-      <c r="BB2" s="80"/>
-      <c r="BC2" s="80"/>
-      <c r="BD2" s="80"/>
-      <c r="BE2" s="80"/>
-      <c r="BF2" s="80"/>
-      <c r="BG2" s="80"/>
-      <c r="BH2" s="80"/>
-      <c r="BI2" s="80"/>
-      <c r="BJ2" s="80"/>
-      <c r="BK2" s="80"/>
-      <c r="BL2" s="80"/>
-      <c r="BM2" s="80"/>
-      <c r="BN2" s="80"/>
-      <c r="BO2" s="80"/>
-      <c r="BP2" s="80"/>
-      <c r="BQ2" s="80"/>
-      <c r="BR2" s="80"/>
-      <c r="BS2" s="80"/>
-      <c r="BT2" s="80"/>
-      <c r="BU2" s="80"/>
-      <c r="BV2" s="80"/>
-      <c r="BW2" s="80"/>
-      <c r="BX2" s="80"/>
-      <c r="BY2" s="80"/>
-      <c r="BZ2" s="80"/>
-      <c r="CA2" s="80"/>
-      <c r="CB2" s="80"/>
-      <c r="CC2" s="80"/>
-      <c r="CD2" s="80"/>
-      <c r="CE2" s="80"/>
-      <c r="CF2" s="80"/>
-      <c r="CG2" s="80"/>
-      <c r="CH2" s="80"/>
-      <c r="CI2" s="80"/>
-      <c r="CJ2" s="80"/>
-      <c r="CK2" s="80"/>
-      <c r="CL2" s="80"/>
-      <c r="CM2" s="80"/>
-      <c r="CN2" s="80"/>
-      <c r="CO2" s="80"/>
-      <c r="CP2" s="80"/>
-      <c r="CQ2" s="80"/>
-      <c r="CR2" s="80"/>
-      <c r="CS2" s="80"/>
-      <c r="CT2" s="80"/>
-      <c r="CU2" s="80"/>
-      <c r="CV2" s="80"/>
-      <c r="CW2" s="80"/>
-      <c r="CX2" s="80"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+      <c r="AA2" s="72"/>
+      <c r="AB2" s="72"/>
+      <c r="AC2" s="72"/>
+      <c r="AD2" s="72"/>
+      <c r="AE2" s="72"/>
+      <c r="AF2" s="72"/>
+      <c r="AG2" s="72"/>
+      <c r="AH2" s="72"/>
+      <c r="AI2" s="72"/>
+      <c r="AJ2" s="72"/>
+      <c r="AK2" s="72"/>
+      <c r="AL2" s="72"/>
+      <c r="AM2" s="72"/>
+      <c r="AN2" s="72"/>
+      <c r="AO2" s="72"/>
+      <c r="AP2" s="72"/>
+      <c r="AQ2" s="72"/>
+      <c r="AR2" s="72"/>
+      <c r="AS2" s="72"/>
+      <c r="AT2" s="72"/>
+      <c r="AU2" s="72"/>
+      <c r="AV2" s="72"/>
+      <c r="AW2" s="72"/>
+      <c r="AX2" s="72"/>
+      <c r="AY2" s="72"/>
+      <c r="AZ2" s="72"/>
+      <c r="BA2" s="72"/>
+      <c r="BB2" s="72"/>
+      <c r="BC2" s="72"/>
+      <c r="BD2" s="72"/>
+      <c r="BE2" s="72"/>
+      <c r="BF2" s="72"/>
+      <c r="BG2" s="72"/>
+      <c r="BH2" s="72"/>
+      <c r="BI2" s="72"/>
+      <c r="BJ2" s="72"/>
+      <c r="BK2" s="72"/>
+      <c r="BL2" s="72"/>
+      <c r="BM2" s="72"/>
+      <c r="BN2" s="72"/>
+      <c r="BO2" s="72"/>
+      <c r="BP2" s="72"/>
+      <c r="BQ2" s="72"/>
+      <c r="BR2" s="72"/>
+      <c r="BS2" s="72"/>
+      <c r="BT2" s="72"/>
+      <c r="BU2" s="72"/>
+      <c r="BV2" s="72"/>
+      <c r="BW2" s="72"/>
+      <c r="BX2" s="72"/>
+      <c r="BY2" s="72"/>
+      <c r="BZ2" s="72"/>
+      <c r="CA2" s="72"/>
+      <c r="CB2" s="72"/>
+      <c r="CC2" s="72"/>
+      <c r="CD2" s="72"/>
+      <c r="CE2" s="72"/>
+      <c r="CF2" s="72"/>
+      <c r="CG2" s="72"/>
+      <c r="CH2" s="72"/>
+      <c r="CI2" s="72"/>
+      <c r="CJ2" s="72"/>
+      <c r="CK2" s="72"/>
+      <c r="CL2" s="72"/>
+      <c r="CM2" s="72"/>
+      <c r="CN2" s="72"/>
+      <c r="CO2" s="72"/>
+      <c r="CP2" s="72"/>
+      <c r="CQ2" s="72"/>
+      <c r="CR2" s="72"/>
+      <c r="CS2" s="72"/>
+      <c r="CT2" s="72"/>
+      <c r="CU2" s="72"/>
+      <c r="CV2" s="72"/>
+      <c r="CW2" s="72"/>
+      <c r="CX2" s="72"/>
     </row>
-    <row r="3" spans="5:102" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E3" s="86" t="s">
+    <row r="3" spans="5:102" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="80"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="80"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="80"/>
-      <c r="AK3" s="80"/>
-      <c r="AL3" s="80"/>
-      <c r="AM3" s="80"/>
-      <c r="AN3" s="80"/>
-      <c r="AO3" s="80"/>
-      <c r="AP3" s="80"/>
-      <c r="AQ3" s="80"/>
-      <c r="AR3" s="80"/>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="80"/>
-      <c r="AU3" s="80"/>
-      <c r="AV3" s="80"/>
-      <c r="AW3" s="80"/>
-      <c r="AX3" s="80"/>
-      <c r="AY3" s="80"/>
-      <c r="AZ3" s="80"/>
-      <c r="BA3" s="80"/>
-      <c r="BB3" s="80"/>
-      <c r="BC3" s="80"/>
-      <c r="BD3" s="80"/>
-      <c r="BE3" s="80"/>
-      <c r="BF3" s="80"/>
-      <c r="BG3" s="80"/>
-      <c r="BH3" s="80"/>
-      <c r="BI3" s="80"/>
-      <c r="BJ3" s="80"/>
-      <c r="BK3" s="80"/>
-      <c r="BL3" s="80"/>
-      <c r="BM3" s="80"/>
-      <c r="BN3" s="80"/>
-      <c r="BO3" s="80"/>
-      <c r="BP3" s="80"/>
-      <c r="BQ3" s="80"/>
-      <c r="BR3" s="80"/>
-      <c r="BS3" s="80"/>
-      <c r="BT3" s="80"/>
-      <c r="BU3" s="80"/>
-      <c r="BV3" s="80"/>
-      <c r="BW3" s="80"/>
-      <c r="BX3" s="80"/>
-      <c r="BY3" s="80"/>
-      <c r="BZ3" s="80"/>
-      <c r="CA3" s="80"/>
-      <c r="CB3" s="80"/>
-      <c r="CC3" s="80"/>
-      <c r="CD3" s="80"/>
-      <c r="CE3" s="80"/>
-      <c r="CF3" s="80"/>
-      <c r="CG3" s="80"/>
-      <c r="CH3" s="80"/>
-      <c r="CI3" s="80"/>
-      <c r="CJ3" s="80"/>
-      <c r="CK3" s="80"/>
-      <c r="CL3" s="80"/>
-      <c r="CM3" s="80"/>
-      <c r="CN3" s="80"/>
-      <c r="CO3" s="80"/>
-      <c r="CP3" s="80"/>
-      <c r="CQ3" s="80"/>
-      <c r="CR3" s="80"/>
-      <c r="CS3" s="80"/>
-      <c r="CT3" s="80"/>
-      <c r="CU3" s="80"/>
-      <c r="CV3" s="80"/>
-      <c r="CW3" s="80"/>
-      <c r="CX3" s="80"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
+      <c r="AK3" s="72"/>
+      <c r="AL3" s="72"/>
+      <c r="AM3" s="72"/>
+      <c r="AN3" s="72"/>
+      <c r="AO3" s="72"/>
+      <c r="AP3" s="72"/>
+      <c r="AQ3" s="72"/>
+      <c r="AR3" s="72"/>
+      <c r="AS3" s="72"/>
+      <c r="AT3" s="72"/>
+      <c r="AU3" s="72"/>
+      <c r="AV3" s="72"/>
+      <c r="AW3" s="72"/>
+      <c r="AX3" s="72"/>
+      <c r="AY3" s="72"/>
+      <c r="AZ3" s="72"/>
+      <c r="BA3" s="72"/>
+      <c r="BB3" s="72"/>
+      <c r="BC3" s="72"/>
+      <c r="BD3" s="72"/>
+      <c r="BE3" s="72"/>
+      <c r="BF3" s="72"/>
+      <c r="BG3" s="72"/>
+      <c r="BH3" s="72"/>
+      <c r="BI3" s="72"/>
+      <c r="BJ3" s="72"/>
+      <c r="BK3" s="72"/>
+      <c r="BL3" s="72"/>
+      <c r="BM3" s="72"/>
+      <c r="BN3" s="72"/>
+      <c r="BO3" s="72"/>
+      <c r="BP3" s="72"/>
+      <c r="BQ3" s="72"/>
+      <c r="BR3" s="72"/>
+      <c r="BS3" s="72"/>
+      <c r="BT3" s="72"/>
+      <c r="BU3" s="72"/>
+      <c r="BV3" s="72"/>
+      <c r="BW3" s="72"/>
+      <c r="BX3" s="72"/>
+      <c r="BY3" s="72"/>
+      <c r="BZ3" s="72"/>
+      <c r="CA3" s="72"/>
+      <c r="CB3" s="72"/>
+      <c r="CC3" s="72"/>
+      <c r="CD3" s="72"/>
+      <c r="CE3" s="72"/>
+      <c r="CF3" s="72"/>
+      <c r="CG3" s="72"/>
+      <c r="CH3" s="72"/>
+      <c r="CI3" s="72"/>
+      <c r="CJ3" s="72"/>
+      <c r="CK3" s="72"/>
+      <c r="CL3" s="72"/>
+      <c r="CM3" s="72"/>
+      <c r="CN3" s="72"/>
+      <c r="CO3" s="72"/>
+      <c r="CP3" s="72"/>
+      <c r="CQ3" s="72"/>
+      <c r="CR3" s="72"/>
+      <c r="CS3" s="72"/>
+      <c r="CT3" s="72"/>
+      <c r="CU3" s="72"/>
+      <c r="CV3" s="72"/>
+      <c r="CW3" s="72"/>
+      <c r="CX3" s="72"/>
     </row>
-    <row r="4" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E4" s="90" t="s">
+    <row r="4" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="80"/>
-      <c r="AC4" s="80"/>
-      <c r="AD4" s="80"/>
-      <c r="AE4" s="80"/>
-      <c r="AF4" s="80"/>
-      <c r="AG4" s="80"/>
-      <c r="AH4" s="80"/>
-      <c r="AI4" s="80"/>
-      <c r="AJ4" s="80"/>
-      <c r="AK4" s="80"/>
-      <c r="AL4" s="80"/>
-      <c r="AM4" s="80"/>
-      <c r="AN4" s="80"/>
-      <c r="AO4" s="80"/>
-      <c r="AP4" s="80"/>
-      <c r="AQ4" s="80"/>
-      <c r="AR4" s="80"/>
-      <c r="AS4" s="80"/>
-      <c r="AT4" s="80"/>
-      <c r="AU4" s="80"/>
-      <c r="AV4" s="80"/>
-      <c r="AW4" s="80"/>
-      <c r="AX4" s="80"/>
-      <c r="AY4" s="80"/>
-      <c r="AZ4" s="80"/>
-      <c r="BA4" s="80"/>
-      <c r="BB4" s="80"/>
-      <c r="BC4" s="80"/>
-      <c r="BD4" s="80"/>
-      <c r="BE4" s="80"/>
-      <c r="BF4" s="80"/>
-      <c r="BG4" s="80"/>
-      <c r="BH4" s="80"/>
-      <c r="BI4" s="80"/>
-      <c r="BJ4" s="80"/>
-      <c r="BK4" s="80"/>
-      <c r="BL4" s="80"/>
-      <c r="BM4" s="80"/>
-      <c r="BN4" s="80"/>
-      <c r="BO4" s="80"/>
-      <c r="BP4" s="80"/>
-      <c r="BQ4" s="80"/>
-      <c r="BR4" s="80"/>
-      <c r="BS4" s="80"/>
-      <c r="BT4" s="80"/>
-      <c r="BU4" s="80"/>
-      <c r="BV4" s="80"/>
-      <c r="BW4" s="80"/>
-      <c r="BX4" s="80"/>
-      <c r="BY4" s="80"/>
-      <c r="BZ4" s="80"/>
-      <c r="CA4" s="80"/>
-      <c r="CB4" s="80"/>
-      <c r="CC4" s="80"/>
-      <c r="CD4" s="80"/>
-      <c r="CE4" s="80"/>
-      <c r="CF4" s="80"/>
-      <c r="CG4" s="80"/>
-      <c r="CH4" s="80"/>
-      <c r="CI4" s="80"/>
-      <c r="CJ4" s="80"/>
-      <c r="CK4" s="80"/>
-      <c r="CL4" s="80"/>
-      <c r="CM4" s="80"/>
-      <c r="CN4" s="80"/>
-      <c r="CO4" s="80"/>
-      <c r="CP4" s="80"/>
-      <c r="CQ4" s="80"/>
-      <c r="CR4" s="80"/>
-      <c r="CS4" s="80"/>
-      <c r="CT4" s="80"/>
-      <c r="CU4" s="80"/>
-      <c r="CV4" s="80"/>
-      <c r="CW4" s="80"/>
-      <c r="CX4" s="80"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="72"/>
+      <c r="Y4" s="72"/>
+      <c r="Z4" s="72"/>
+      <c r="AA4" s="72"/>
+      <c r="AB4" s="72"/>
+      <c r="AC4" s="72"/>
+      <c r="AD4" s="72"/>
+      <c r="AE4" s="72"/>
+      <c r="AF4" s="72"/>
+      <c r="AG4" s="72"/>
+      <c r="AH4" s="72"/>
+      <c r="AI4" s="72"/>
+      <c r="AJ4" s="72"/>
+      <c r="AK4" s="72"/>
+      <c r="AL4" s="72"/>
+      <c r="AM4" s="72"/>
+      <c r="AN4" s="72"/>
+      <c r="AO4" s="72"/>
+      <c r="AP4" s="72"/>
+      <c r="AQ4" s="72"/>
+      <c r="AR4" s="72"/>
+      <c r="AS4" s="72"/>
+      <c r="AT4" s="72"/>
+      <c r="AU4" s="72"/>
+      <c r="AV4" s="72"/>
+      <c r="AW4" s="72"/>
+      <c r="AX4" s="72"/>
+      <c r="AY4" s="72"/>
+      <c r="AZ4" s="72"/>
+      <c r="BA4" s="72"/>
+      <c r="BB4" s="72"/>
+      <c r="BC4" s="72"/>
+      <c r="BD4" s="72"/>
+      <c r="BE4" s="72"/>
+      <c r="BF4" s="72"/>
+      <c r="BG4" s="72"/>
+      <c r="BH4" s="72"/>
+      <c r="BI4" s="72"/>
+      <c r="BJ4" s="72"/>
+      <c r="BK4" s="72"/>
+      <c r="BL4" s="72"/>
+      <c r="BM4" s="72"/>
+      <c r="BN4" s="72"/>
+      <c r="BO4" s="72"/>
+      <c r="BP4" s="72"/>
+      <c r="BQ4" s="72"/>
+      <c r="BR4" s="72"/>
+      <c r="BS4" s="72"/>
+      <c r="BT4" s="72"/>
+      <c r="BU4" s="72"/>
+      <c r="BV4" s="72"/>
+      <c r="BW4" s="72"/>
+      <c r="BX4" s="72"/>
+      <c r="BY4" s="72"/>
+      <c r="BZ4" s="72"/>
+      <c r="CA4" s="72"/>
+      <c r="CB4" s="72"/>
+      <c r="CC4" s="72"/>
+      <c r="CD4" s="72"/>
+      <c r="CE4" s="72"/>
+      <c r="CF4" s="72"/>
+      <c r="CG4" s="72"/>
+      <c r="CH4" s="72"/>
+      <c r="CI4" s="72"/>
+      <c r="CJ4" s="72"/>
+      <c r="CK4" s="72"/>
+      <c r="CL4" s="72"/>
+      <c r="CM4" s="72"/>
+      <c r="CN4" s="72"/>
+      <c r="CO4" s="72"/>
+      <c r="CP4" s="72"/>
+      <c r="CQ4" s="72"/>
+      <c r="CR4" s="72"/>
+      <c r="CS4" s="72"/>
+      <c r="CT4" s="72"/>
+      <c r="CU4" s="72"/>
+      <c r="CV4" s="72"/>
+      <c r="CW4" s="72"/>
+      <c r="CX4" s="72"/>
     </row>
-    <row r="5" spans="5:102" x14ac:dyDescent="0.25">
+    <row r="5" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -1888,115 +1896,115 @@
       <c r="CW5" s="2"/>
       <c r="CX5" s="2"/>
     </row>
-    <row r="6" spans="5:102" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="94" t="s">
+    <row r="6" spans="5:102" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
-      <c r="S6" s="80"/>
-      <c r="T6" s="80"/>
-      <c r="U6" s="80"/>
-      <c r="V6" s="80"/>
-      <c r="W6" s="80"/>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="80"/>
-      <c r="Z6" s="80"/>
-      <c r="AA6" s="80"/>
-      <c r="AB6" s="80"/>
-      <c r="AC6" s="80"/>
-      <c r="AD6" s="80"/>
-      <c r="AE6" s="80"/>
-      <c r="AF6" s="80"/>
-      <c r="AG6" s="80"/>
-      <c r="AH6" s="80"/>
-      <c r="AI6" s="80"/>
-      <c r="AJ6" s="80"/>
-      <c r="AK6" s="80"/>
-      <c r="AL6" s="80"/>
-      <c r="AM6" s="80"/>
-      <c r="AN6" s="80"/>
-      <c r="AO6" s="80"/>
-      <c r="AP6" s="80"/>
-      <c r="AQ6" s="80"/>
-      <c r="AR6" s="80"/>
-      <c r="AS6" s="80"/>
-      <c r="AT6" s="80"/>
-      <c r="AU6" s="80"/>
-      <c r="AV6" s="80"/>
-      <c r="AW6" s="80"/>
-      <c r="AX6" s="80"/>
-      <c r="AY6" s="80"/>
-      <c r="AZ6" s="80"/>
-      <c r="BA6" s="80"/>
-      <c r="BB6" s="80"/>
-      <c r="BC6" s="80"/>
-      <c r="BD6" s="80"/>
-      <c r="BE6" s="80"/>
-      <c r="BF6" s="80"/>
-      <c r="BG6" s="80"/>
-      <c r="BH6" s="80"/>
-      <c r="BI6" s="80"/>
-      <c r="BJ6" s="80"/>
-      <c r="BK6" s="80"/>
-      <c r="BL6" s="80"/>
-      <c r="BM6" s="80"/>
-      <c r="BN6" s="80"/>
-      <c r="BO6" s="80"/>
-      <c r="BP6" s="80"/>
-      <c r="BQ6" s="80"/>
-      <c r="BR6" s="80"/>
-      <c r="BS6" s="80"/>
-      <c r="BT6" s="80"/>
-      <c r="BU6" s="80"/>
-      <c r="BV6" s="80"/>
-      <c r="BW6" s="80"/>
-      <c r="BX6" s="80"/>
-      <c r="BY6" s="80"/>
-      <c r="BZ6" s="80"/>
-      <c r="CA6" s="80"/>
-      <c r="CB6" s="80"/>
-      <c r="CC6" s="80"/>
-      <c r="CD6" s="80"/>
-      <c r="CE6" s="80"/>
-      <c r="CF6" s="80"/>
-      <c r="CG6" s="80"/>
-      <c r="CH6" s="80"/>
-      <c r="CI6" s="80"/>
-      <c r="CJ6" s="80"/>
-      <c r="CK6" s="80"/>
-      <c r="CL6" s="80"/>
-      <c r="CM6" s="80"/>
-      <c r="CN6" s="80"/>
-      <c r="CO6" s="80"/>
-      <c r="CP6" s="80"/>
-      <c r="CQ6" s="80"/>
-      <c r="CR6" s="80"/>
-      <c r="CS6" s="80"/>
-      <c r="CT6" s="80"/>
-      <c r="CU6" s="80"/>
-      <c r="CV6" s="80"/>
-      <c r="CW6" s="80"/>
-      <c r="CX6" s="80"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="72"/>
+      <c r="Z6" s="72"/>
+      <c r="AA6" s="72"/>
+      <c r="AB6" s="72"/>
+      <c r="AC6" s="72"/>
+      <c r="AD6" s="72"/>
+      <c r="AE6" s="72"/>
+      <c r="AF6" s="72"/>
+      <c r="AG6" s="72"/>
+      <c r="AH6" s="72"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="72"/>
+      <c r="AK6" s="72"/>
+      <c r="AL6" s="72"/>
+      <c r="AM6" s="72"/>
+      <c r="AN6" s="72"/>
+      <c r="AO6" s="72"/>
+      <c r="AP6" s="72"/>
+      <c r="AQ6" s="72"/>
+      <c r="AR6" s="72"/>
+      <c r="AS6" s="72"/>
+      <c r="AT6" s="72"/>
+      <c r="AU6" s="72"/>
+      <c r="AV6" s="72"/>
+      <c r="AW6" s="72"/>
+      <c r="AX6" s="72"/>
+      <c r="AY6" s="72"/>
+      <c r="AZ6" s="72"/>
+      <c r="BA6" s="72"/>
+      <c r="BB6" s="72"/>
+      <c r="BC6" s="72"/>
+      <c r="BD6" s="72"/>
+      <c r="BE6" s="72"/>
+      <c r="BF6" s="72"/>
+      <c r="BG6" s="72"/>
+      <c r="BH6" s="72"/>
+      <c r="BI6" s="72"/>
+      <c r="BJ6" s="72"/>
+      <c r="BK6" s="72"/>
+      <c r="BL6" s="72"/>
+      <c r="BM6" s="72"/>
+      <c r="BN6" s="72"/>
+      <c r="BO6" s="72"/>
+      <c r="BP6" s="72"/>
+      <c r="BQ6" s="72"/>
+      <c r="BR6" s="72"/>
+      <c r="BS6" s="72"/>
+      <c r="BT6" s="72"/>
+      <c r="BU6" s="72"/>
+      <c r="BV6" s="72"/>
+      <c r="BW6" s="72"/>
+      <c r="BX6" s="72"/>
+      <c r="BY6" s="72"/>
+      <c r="BZ6" s="72"/>
+      <c r="CA6" s="72"/>
+      <c r="CB6" s="72"/>
+      <c r="CC6" s="72"/>
+      <c r="CD6" s="72"/>
+      <c r="CE6" s="72"/>
+      <c r="CF6" s="72"/>
+      <c r="CG6" s="72"/>
+      <c r="CH6" s="72"/>
+      <c r="CI6" s="72"/>
+      <c r="CJ6" s="72"/>
+      <c r="CK6" s="72"/>
+      <c r="CL6" s="72"/>
+      <c r="CM6" s="72"/>
+      <c r="CN6" s="72"/>
+      <c r="CO6" s="72"/>
+      <c r="CP6" s="72"/>
+      <c r="CQ6" s="72"/>
+      <c r="CR6" s="72"/>
+      <c r="CS6" s="72"/>
+      <c r="CT6" s="72"/>
+      <c r="CU6" s="72"/>
+      <c r="CV6" s="72"/>
+      <c r="CW6" s="72"/>
+      <c r="CX6" s="72"/>
     </row>
-    <row r="7" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E7" s="83" t="s">
+    <row r="7" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E7" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="80"/>
+      <c r="F7" s="72"/>
       <c r="G7" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
@@ -2009,56 +2017,56 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="79"/>
-      <c r="T7" s="80"/>
-      <c r="U7" s="80"/>
-      <c r="V7" s="80"/>
-      <c r="W7" s="80"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="72"/>
+      <c r="V7" s="72"/>
+      <c r="W7" s="72"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="6"/>
-      <c r="AC7" s="79"/>
-      <c r="AD7" s="80"/>
-      <c r="AE7" s="80"/>
-      <c r="AF7" s="80"/>
-      <c r="AG7" s="80"/>
-      <c r="AH7" s="80"/>
-      <c r="AI7" s="80"/>
-      <c r="AJ7" s="80"/>
-      <c r="AK7" s="80"/>
-      <c r="AL7" s="80"/>
-      <c r="AM7" s="80"/>
-      <c r="AN7" s="80"/>
-      <c r="AO7" s="80"/>
-      <c r="AP7" s="80"/>
-      <c r="AQ7" s="80"/>
-      <c r="AR7" s="80"/>
-      <c r="AS7" s="80"/>
-      <c r="AT7" s="80"/>
-      <c r="AU7" s="80"/>
-      <c r="AV7" s="80"/>
-      <c r="AW7" s="80"/>
-      <c r="AX7" s="80"/>
-      <c r="AY7" s="80"/>
-      <c r="AZ7" s="80"/>
-      <c r="BA7" s="80"/>
-      <c r="BB7" s="80"/>
-      <c r="BC7" s="80"/>
-      <c r="BD7" s="80"/>
-      <c r="BE7" s="80"/>
-      <c r="BF7" s="80"/>
-      <c r="BG7" s="80"/>
-      <c r="BH7" s="80"/>
-      <c r="BI7" s="80"/>
-      <c r="BJ7" s="80"/>
-      <c r="BK7" s="80"/>
-      <c r="BL7" s="80"/>
-      <c r="BM7" s="80"/>
-      <c r="BN7" s="80"/>
-      <c r="BO7" s="80"/>
-      <c r="BP7" s="80"/>
+      <c r="AC7" s="82"/>
+      <c r="AD7" s="72"/>
+      <c r="AE7" s="72"/>
+      <c r="AF7" s="72"/>
+      <c r="AG7" s="72"/>
+      <c r="AH7" s="72"/>
+      <c r="AI7" s="72"/>
+      <c r="AJ7" s="72"/>
+      <c r="AK7" s="72"/>
+      <c r="AL7" s="72"/>
+      <c r="AM7" s="72"/>
+      <c r="AN7" s="72"/>
+      <c r="AO7" s="72"/>
+      <c r="AP7" s="72"/>
+      <c r="AQ7" s="72"/>
+      <c r="AR7" s="72"/>
+      <c r="AS7" s="72"/>
+      <c r="AT7" s="72"/>
+      <c r="AU7" s="72"/>
+      <c r="AV7" s="72"/>
+      <c r="AW7" s="72"/>
+      <c r="AX7" s="72"/>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="72"/>
+      <c r="BA7" s="72"/>
+      <c r="BB7" s="72"/>
+      <c r="BC7" s="72"/>
+      <c r="BD7" s="72"/>
+      <c r="BE7" s="72"/>
+      <c r="BF7" s="72"/>
+      <c r="BG7" s="72"/>
+      <c r="BH7" s="72"/>
+      <c r="BI7" s="72"/>
+      <c r="BJ7" s="72"/>
+      <c r="BK7" s="72"/>
+      <c r="BL7" s="72"/>
+      <c r="BM7" s="72"/>
+      <c r="BN7" s="72"/>
+      <c r="BO7" s="72"/>
+      <c r="BP7" s="72"/>
       <c r="BQ7" s="5"/>
       <c r="BR7" s="5"/>
       <c r="BS7" s="5"/>
@@ -2094,11 +2102,11 @@
       <c r="CW7" s="2"/>
       <c r="CX7" s="2"/>
     </row>
-    <row r="8" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E8" s="83" t="s">
+    <row r="8" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E8" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="80"/>
+      <c r="F8" s="72"/>
       <c r="G8" s="7" t="s">
         <v>45</v>
       </c>
@@ -2113,56 +2121,56 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="80"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="79"/>
-      <c r="AD8" s="80"/>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="80"/>
-      <c r="AG8" s="80"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="80"/>
-      <c r="AJ8" s="80"/>
-      <c r="AK8" s="80"/>
-      <c r="AL8" s="80"/>
-      <c r="AM8" s="80"/>
-      <c r="AN8" s="80"/>
-      <c r="AO8" s="80"/>
-      <c r="AP8" s="80"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="80"/>
-      <c r="AS8" s="80"/>
-      <c r="AT8" s="80"/>
-      <c r="AU8" s="80"/>
-      <c r="AV8" s="80"/>
-      <c r="AW8" s="80"/>
-      <c r="AX8" s="80"/>
-      <c r="AY8" s="80"/>
-      <c r="AZ8" s="80"/>
-      <c r="BA8" s="80"/>
-      <c r="BB8" s="80"/>
-      <c r="BC8" s="80"/>
-      <c r="BD8" s="80"/>
-      <c r="BE8" s="80"/>
-      <c r="BF8" s="80"/>
-      <c r="BG8" s="80"/>
-      <c r="BH8" s="80"/>
-      <c r="BI8" s="80"/>
-      <c r="BJ8" s="80"/>
-      <c r="BK8" s="80"/>
-      <c r="BL8" s="80"/>
-      <c r="BM8" s="80"/>
-      <c r="BN8" s="80"/>
-      <c r="BO8" s="80"/>
-      <c r="BP8" s="80"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="72"/>
+      <c r="AE8" s="72"/>
+      <c r="AF8" s="72"/>
+      <c r="AG8" s="72"/>
+      <c r="AH8" s="72"/>
+      <c r="AI8" s="72"/>
+      <c r="AJ8" s="72"/>
+      <c r="AK8" s="72"/>
+      <c r="AL8" s="72"/>
+      <c r="AM8" s="72"/>
+      <c r="AN8" s="72"/>
+      <c r="AO8" s="72"/>
+      <c r="AP8" s="72"/>
+      <c r="AQ8" s="72"/>
+      <c r="AR8" s="72"/>
+      <c r="AS8" s="72"/>
+      <c r="AT8" s="72"/>
+      <c r="AU8" s="72"/>
+      <c r="AV8" s="72"/>
+      <c r="AW8" s="72"/>
+      <c r="AX8" s="72"/>
+      <c r="AY8" s="72"/>
+      <c r="AZ8" s="72"/>
+      <c r="BA8" s="72"/>
+      <c r="BB8" s="72"/>
+      <c r="BC8" s="72"/>
+      <c r="BD8" s="72"/>
+      <c r="BE8" s="72"/>
+      <c r="BF8" s="72"/>
+      <c r="BG8" s="72"/>
+      <c r="BH8" s="72"/>
+      <c r="BI8" s="72"/>
+      <c r="BJ8" s="72"/>
+      <c r="BK8" s="72"/>
+      <c r="BL8" s="72"/>
+      <c r="BM8" s="72"/>
+      <c r="BN8" s="72"/>
+      <c r="BO8" s="72"/>
+      <c r="BP8" s="72"/>
       <c r="BQ8" s="5"/>
       <c r="BR8" s="5"/>
       <c r="BS8" s="5"/>
@@ -2198,13 +2206,13 @@
       <c r="CW8" s="2"/>
       <c r="CX8" s="2"/>
     </row>
-    <row r="9" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E9" s="83" t="s">
+    <row r="9" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E9" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="80"/>
+      <c r="F9" s="72"/>
       <c r="G9" s="7" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="3"/>
@@ -2217,56 +2225,56 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="6"/>
-      <c r="S9" s="79"/>
-      <c r="T9" s="80"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="80"/>
-      <c r="W9" s="80"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="6"/>
-      <c r="AC9" s="79"/>
-      <c r="AD9" s="80"/>
-      <c r="AE9" s="80"/>
-      <c r="AF9" s="80"/>
-      <c r="AG9" s="80"/>
-      <c r="AH9" s="80"/>
-      <c r="AI9" s="80"/>
-      <c r="AJ9" s="80"/>
-      <c r="AK9" s="80"/>
-      <c r="AL9" s="80"/>
-      <c r="AM9" s="80"/>
-      <c r="AN9" s="80"/>
-      <c r="AO9" s="80"/>
-      <c r="AP9" s="80"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="80"/>
-      <c r="AS9" s="80"/>
-      <c r="AT9" s="80"/>
-      <c r="AU9" s="80"/>
-      <c r="AV9" s="80"/>
-      <c r="AW9" s="80"/>
-      <c r="AX9" s="80"/>
-      <c r="AY9" s="80"/>
-      <c r="AZ9" s="80"/>
-      <c r="BA9" s="80"/>
-      <c r="BB9" s="80"/>
-      <c r="BC9" s="80"/>
-      <c r="BD9" s="80"/>
-      <c r="BE9" s="80"/>
-      <c r="BF9" s="80"/>
-      <c r="BG9" s="80"/>
-      <c r="BH9" s="80"/>
-      <c r="BI9" s="80"/>
-      <c r="BJ9" s="80"/>
-      <c r="BK9" s="80"/>
-      <c r="BL9" s="80"/>
-      <c r="BM9" s="80"/>
-      <c r="BN9" s="80"/>
-      <c r="BO9" s="80"/>
-      <c r="BP9" s="80"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="72"/>
+      <c r="AF9" s="72"/>
+      <c r="AG9" s="72"/>
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="72"/>
+      <c r="AJ9" s="72"/>
+      <c r="AK9" s="72"/>
+      <c r="AL9" s="72"/>
+      <c r="AM9" s="72"/>
+      <c r="AN9" s="72"/>
+      <c r="AO9" s="72"/>
+      <c r="AP9" s="72"/>
+      <c r="AQ9" s="72"/>
+      <c r="AR9" s="72"/>
+      <c r="AS9" s="72"/>
+      <c r="AT9" s="72"/>
+      <c r="AU9" s="72"/>
+      <c r="AV9" s="72"/>
+      <c r="AW9" s="72"/>
+      <c r="AX9" s="72"/>
+      <c r="AY9" s="72"/>
+      <c r="AZ9" s="72"/>
+      <c r="BA9" s="72"/>
+      <c r="BB9" s="72"/>
+      <c r="BC9" s="72"/>
+      <c r="BD9" s="72"/>
+      <c r="BE9" s="72"/>
+      <c r="BF9" s="72"/>
+      <c r="BG9" s="72"/>
+      <c r="BH9" s="72"/>
+      <c r="BI9" s="72"/>
+      <c r="BJ9" s="72"/>
+      <c r="BK9" s="72"/>
+      <c r="BL9" s="72"/>
+      <c r="BM9" s="72"/>
+      <c r="BN9" s="72"/>
+      <c r="BO9" s="72"/>
+      <c r="BP9" s="72"/>
       <c r="BQ9" s="5"/>
       <c r="BR9" s="5"/>
       <c r="BS9" s="5"/>
@@ -2302,18 +2310,18 @@
       <c r="CW9" s="2"/>
       <c r="CX9" s="2"/>
     </row>
-    <row r="10" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E10" s="83" t="s">
+    <row r="10" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E10" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="72"/>
+      <c r="G10" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="85"/>
+      <c r="K10" s="79"/>
       <c r="L10" s="77"/>
       <c r="M10" s="77"/>
       <c r="N10" s="77"/>
@@ -2321,13 +2329,13 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="84" t="s">
+      <c r="S10" s="81" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="79" t="s">
         <v>10</v>
-      </c>
-      <c r="T10" s="80"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="85" t="s">
-        <v>11</v>
       </c>
       <c r="W10" s="77"/>
       <c r="X10" s="77"/>
@@ -2335,46 +2343,46 @@
       <c r="Z10" s="77"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="6"/>
-      <c r="AC10" s="79"/>
-      <c r="AD10" s="80"/>
-      <c r="AE10" s="80"/>
-      <c r="AF10" s="80"/>
-      <c r="AG10" s="80"/>
-      <c r="AH10" s="80"/>
-      <c r="AI10" s="80"/>
-      <c r="AJ10" s="80"/>
-      <c r="AK10" s="80"/>
-      <c r="AL10" s="80"/>
-      <c r="AM10" s="80"/>
-      <c r="AN10" s="80"/>
-      <c r="AO10" s="80"/>
-      <c r="AP10" s="80"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="80"/>
-      <c r="AS10" s="80"/>
-      <c r="AT10" s="80"/>
-      <c r="AU10" s="80"/>
-      <c r="AV10" s="80"/>
-      <c r="AW10" s="80"/>
-      <c r="AX10" s="80"/>
-      <c r="AY10" s="80"/>
-      <c r="AZ10" s="80"/>
-      <c r="BA10" s="80"/>
-      <c r="BB10" s="80"/>
-      <c r="BC10" s="80"/>
-      <c r="BD10" s="80"/>
-      <c r="BE10" s="80"/>
-      <c r="BF10" s="80"/>
-      <c r="BG10" s="80"/>
-      <c r="BH10" s="80"/>
-      <c r="BI10" s="80"/>
-      <c r="BJ10" s="80"/>
-      <c r="BK10" s="80"/>
-      <c r="BL10" s="80"/>
-      <c r="BM10" s="80"/>
-      <c r="BN10" s="80"/>
-      <c r="BO10" s="80"/>
-      <c r="BP10" s="80"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="72"/>
+      <c r="AL10" s="72"/>
+      <c r="AM10" s="72"/>
+      <c r="AN10" s="72"/>
+      <c r="AO10" s="72"/>
+      <c r="AP10" s="72"/>
+      <c r="AQ10" s="72"/>
+      <c r="AR10" s="72"/>
+      <c r="AS10" s="72"/>
+      <c r="AT10" s="72"/>
+      <c r="AU10" s="72"/>
+      <c r="AV10" s="72"/>
+      <c r="AW10" s="72"/>
+      <c r="AX10" s="72"/>
+      <c r="AY10" s="72"/>
+      <c r="AZ10" s="72"/>
+      <c r="BA10" s="72"/>
+      <c r="BB10" s="72"/>
+      <c r="BC10" s="72"/>
+      <c r="BD10" s="72"/>
+      <c r="BE10" s="72"/>
+      <c r="BF10" s="72"/>
+      <c r="BG10" s="72"/>
+      <c r="BH10" s="72"/>
+      <c r="BI10" s="72"/>
+      <c r="BJ10" s="72"/>
+      <c r="BK10" s="72"/>
+      <c r="BL10" s="72"/>
+      <c r="BM10" s="72"/>
+      <c r="BN10" s="72"/>
+      <c r="BO10" s="72"/>
+      <c r="BP10" s="72"/>
       <c r="BQ10" s="5"/>
       <c r="BR10" s="5"/>
       <c r="BS10" s="5"/>
@@ -2410,13 +2418,13 @@
       <c r="CW10" s="2"/>
       <c r="CX10" s="2"/>
     </row>
-    <row r="11" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E11" s="83" t="s">
+    <row r="11" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E11" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="72"/>
+      <c r="G11" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="F11" s="80"/>
-      <c r="G11" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
@@ -2429,22 +2437,22 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="6"/>
-      <c r="S11" s="84" t="s">
+      <c r="S11" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
+      <c r="V11" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="80"/>
-      <c r="U11" s="80"/>
-      <c r="V11" s="87" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
+      <c r="W11" s="95"/>
+      <c r="X11" s="95"/>
+      <c r="Y11" s="95"/>
+      <c r="Z11" s="95"/>
       <c r="AA11" s="2"/>
-      <c r="AB11" s="84"/>
-      <c r="AC11" s="80"/>
-      <c r="AD11" s="80"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="72"/>
+      <c r="AD11" s="72"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="5"/>
       <c r="AG11" s="5"/>
@@ -2483,8 +2491,8 @@
       <c r="BN11" s="5"/>
       <c r="BO11" s="5"/>
       <c r="BP11" s="5"/>
-      <c r="BQ11" s="89"/>
-      <c r="BR11" s="80"/>
+      <c r="BQ11" s="96"/>
+      <c r="BR11" s="72"/>
       <c r="BS11" s="5"/>
       <c r="BT11" s="2"/>
       <c r="BU11" s="2"/>
@@ -2518,40 +2526,40 @@
       <c r="CW11" s="2"/>
       <c r="CX11" s="2"/>
     </row>
-    <row r="12" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E12" s="96" t="s">
+    <row r="12" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E12" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="F12" s="74"/>
-      <c r="G12" s="10" t="s">
-        <v>17</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="84"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
       <c r="V12" s="13">
         <v>0.5</v>
       </c>
-      <c r="X12" s="97"/>
-      <c r="Y12" s="74"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="84"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="14"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="74"/>
-      <c r="AD12" s="74"/>
+      <c r="AB12" s="99"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="84"/>
       <c r="AE12" s="15"/>
       <c r="AF12" s="10"/>
       <c r="AG12" s="10"/>
@@ -2590,8 +2598,8 @@
       <c r="BN12" s="10"/>
       <c r="BO12" s="10"/>
       <c r="BP12" s="10"/>
-      <c r="BQ12" s="97"/>
-      <c r="BR12" s="74"/>
+      <c r="BQ12" s="86"/>
+      <c r="BR12" s="84"/>
       <c r="BS12" s="10"/>
       <c r="BT12" s="14"/>
       <c r="BU12" s="2"/>
@@ -2625,216 +2633,216 @@
       <c r="CW12" s="2"/>
       <c r="CX12" s="2"/>
     </row>
-    <row r="13" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="91" t="s">
+    <row r="13" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="91" t="s">
+      <c r="G13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="98"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
-      <c r="U13" s="71"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="71"/>
-      <c r="X13" s="71"/>
-      <c r="Y13" s="71"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="71"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="71"/>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="71"/>
-      <c r="AH13" s="71"/>
-      <c r="AI13" s="71"/>
-      <c r="AJ13" s="71"/>
-      <c r="AK13" s="71"/>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="71"/>
-      <c r="AN13" s="71"/>
-      <c r="AO13" s="71"/>
-      <c r="AP13" s="71"/>
-      <c r="AQ13" s="71"/>
-      <c r="AR13" s="71"/>
-      <c r="AS13" s="71"/>
-      <c r="AT13" s="71"/>
-      <c r="AU13" s="71"/>
-      <c r="AV13" s="71"/>
-      <c r="AW13" s="71"/>
-      <c r="AX13" s="71"/>
-      <c r="AY13" s="71"/>
-      <c r="AZ13" s="71"/>
-      <c r="BA13" s="71"/>
-      <c r="BB13" s="71"/>
-      <c r="BC13" s="71"/>
-      <c r="BD13" s="71"/>
-      <c r="BE13" s="71"/>
-      <c r="BF13" s="71"/>
-      <c r="BG13" s="71"/>
-      <c r="BH13" s="71"/>
-      <c r="BI13" s="71"/>
-      <c r="BJ13" s="71"/>
-      <c r="BK13" s="71"/>
-      <c r="BL13" s="71"/>
-      <c r="BM13" s="71"/>
-      <c r="BN13" s="71"/>
-      <c r="BO13" s="71"/>
-      <c r="BP13" s="71"/>
-      <c r="BQ13" s="71"/>
-      <c r="BR13" s="71"/>
-      <c r="BS13" s="71"/>
-      <c r="BT13" s="72"/>
-      <c r="BU13" s="78"/>
-      <c r="BV13" s="71"/>
-      <c r="BW13" s="71"/>
-      <c r="BX13" s="71"/>
-      <c r="BY13" s="71"/>
-      <c r="BZ13" s="71"/>
-      <c r="CA13" s="71"/>
-      <c r="CB13" s="71"/>
-      <c r="CC13" s="71"/>
-      <c r="CD13" s="71"/>
-      <c r="CE13" s="71"/>
-      <c r="CF13" s="71"/>
-      <c r="CG13" s="71"/>
-      <c r="CH13" s="71"/>
-      <c r="CI13" s="71"/>
-      <c r="CJ13" s="71"/>
-      <c r="CK13" s="71"/>
-      <c r="CL13" s="71"/>
-      <c r="CM13" s="71"/>
-      <c r="CN13" s="71"/>
-      <c r="CO13" s="70"/>
-      <c r="CP13" s="71"/>
-      <c r="CQ13" s="71"/>
-      <c r="CR13" s="71"/>
-      <c r="CS13" s="71"/>
-      <c r="CT13" s="71"/>
-      <c r="CU13" s="71"/>
-      <c r="CV13" s="71"/>
-      <c r="CW13" s="71"/>
-      <c r="CX13" s="72"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="88"/>
+      <c r="AF13" s="88"/>
+      <c r="AG13" s="88"/>
+      <c r="AH13" s="88"/>
+      <c r="AI13" s="88"/>
+      <c r="AJ13" s="88"/>
+      <c r="AK13" s="88"/>
+      <c r="AL13" s="88"/>
+      <c r="AM13" s="88"/>
+      <c r="AN13" s="88"/>
+      <c r="AO13" s="88"/>
+      <c r="AP13" s="88"/>
+      <c r="AQ13" s="88"/>
+      <c r="AR13" s="88"/>
+      <c r="AS13" s="88"/>
+      <c r="AT13" s="88"/>
+      <c r="AU13" s="88"/>
+      <c r="AV13" s="88"/>
+      <c r="AW13" s="88"/>
+      <c r="AX13" s="88"/>
+      <c r="AY13" s="88"/>
+      <c r="AZ13" s="88"/>
+      <c r="BA13" s="88"/>
+      <c r="BB13" s="88"/>
+      <c r="BC13" s="88"/>
+      <c r="BD13" s="88"/>
+      <c r="BE13" s="88"/>
+      <c r="BF13" s="88"/>
+      <c r="BG13" s="88"/>
+      <c r="BH13" s="88"/>
+      <c r="BI13" s="88"/>
+      <c r="BJ13" s="88"/>
+      <c r="BK13" s="88"/>
+      <c r="BL13" s="88"/>
+      <c r="BM13" s="88"/>
+      <c r="BN13" s="88"/>
+      <c r="BO13" s="88"/>
+      <c r="BP13" s="88"/>
+      <c r="BQ13" s="88"/>
+      <c r="BR13" s="88"/>
+      <c r="BS13" s="88"/>
+      <c r="BT13" s="89"/>
+      <c r="BU13" s="98"/>
+      <c r="BV13" s="88"/>
+      <c r="BW13" s="88"/>
+      <c r="BX13" s="88"/>
+      <c r="BY13" s="88"/>
+      <c r="BZ13" s="88"/>
+      <c r="CA13" s="88"/>
+      <c r="CB13" s="88"/>
+      <c r="CC13" s="88"/>
+      <c r="CD13" s="88"/>
+      <c r="CE13" s="88"/>
+      <c r="CF13" s="88"/>
+      <c r="CG13" s="88"/>
+      <c r="CH13" s="88"/>
+      <c r="CI13" s="88"/>
+      <c r="CJ13" s="88"/>
+      <c r="CK13" s="88"/>
+      <c r="CL13" s="88"/>
+      <c r="CM13" s="88"/>
+      <c r="CN13" s="88"/>
+      <c r="CO13" s="97"/>
+      <c r="CP13" s="88"/>
+      <c r="CQ13" s="88"/>
+      <c r="CR13" s="88"/>
+      <c r="CS13" s="88"/>
+      <c r="CT13" s="88"/>
+      <c r="CU13" s="88"/>
+      <c r="CV13" s="88"/>
+      <c r="CW13" s="88"/>
+      <c r="CX13" s="89"/>
     </row>
-    <row r="14" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74"/>
-      <c r="X14" s="74"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="74"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="74"/>
-      <c r="AF14" s="74"/>
-      <c r="AG14" s="74"/>
-      <c r="AH14" s="74"/>
-      <c r="AI14" s="74"/>
-      <c r="AJ14" s="74"/>
-      <c r="AK14" s="74"/>
-      <c r="AL14" s="74"/>
-      <c r="AM14" s="74"/>
-      <c r="AN14" s="74"/>
-      <c r="AO14" s="74"/>
-      <c r="AP14" s="74"/>
-      <c r="AQ14" s="74"/>
-      <c r="AR14" s="74"/>
-      <c r="AS14" s="74"/>
-      <c r="AT14" s="74"/>
-      <c r="AU14" s="74"/>
-      <c r="AV14" s="74"/>
-      <c r="AW14" s="74"/>
-      <c r="AX14" s="74"/>
-      <c r="AY14" s="74"/>
-      <c r="AZ14" s="74"/>
-      <c r="BA14" s="74"/>
-      <c r="BB14" s="74"/>
-      <c r="BC14" s="74"/>
-      <c r="BD14" s="74"/>
-      <c r="BE14" s="74"/>
-      <c r="BF14" s="74"/>
-      <c r="BG14" s="74"/>
-      <c r="BH14" s="74"/>
-      <c r="BI14" s="74"/>
-      <c r="BJ14" s="74"/>
-      <c r="BK14" s="74"/>
-      <c r="BL14" s="74"/>
-      <c r="BM14" s="74"/>
-      <c r="BN14" s="74"/>
-      <c r="BO14" s="74"/>
-      <c r="BP14" s="74"/>
-      <c r="BQ14" s="74"/>
-      <c r="BR14" s="74"/>
-      <c r="BS14" s="74"/>
-      <c r="BT14" s="75"/>
-      <c r="BU14" s="73"/>
-      <c r="BV14" s="74"/>
-      <c r="BW14" s="74"/>
-      <c r="BX14" s="74"/>
-      <c r="BY14" s="74"/>
-      <c r="BZ14" s="74"/>
-      <c r="CA14" s="74"/>
-      <c r="CB14" s="74"/>
-      <c r="CC14" s="74"/>
-      <c r="CD14" s="74"/>
-      <c r="CE14" s="74"/>
-      <c r="CF14" s="74"/>
-      <c r="CG14" s="74"/>
-      <c r="CH14" s="74"/>
-      <c r="CI14" s="74"/>
-      <c r="CJ14" s="74"/>
-      <c r="CK14" s="74"/>
-      <c r="CL14" s="74"/>
-      <c r="CM14" s="74"/>
-      <c r="CN14" s="74"/>
-      <c r="CO14" s="73"/>
-      <c r="CP14" s="74"/>
-      <c r="CQ14" s="74"/>
-      <c r="CR14" s="74"/>
-      <c r="CS14" s="74"/>
-      <c r="CT14" s="74"/>
-      <c r="CU14" s="74"/>
-      <c r="CV14" s="74"/>
-      <c r="CW14" s="74"/>
-      <c r="CX14" s="75"/>
+    <row r="14" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
+      <c r="T14" s="84"/>
+      <c r="U14" s="84"/>
+      <c r="V14" s="84"/>
+      <c r="W14" s="84"/>
+      <c r="X14" s="84"/>
+      <c r="Y14" s="84"/>
+      <c r="Z14" s="84"/>
+      <c r="AA14" s="84"/>
+      <c r="AB14" s="84"/>
+      <c r="AC14" s="84"/>
+      <c r="AD14" s="84"/>
+      <c r="AE14" s="84"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="84"/>
+      <c r="AH14" s="84"/>
+      <c r="AI14" s="84"/>
+      <c r="AJ14" s="84"/>
+      <c r="AK14" s="84"/>
+      <c r="AL14" s="84"/>
+      <c r="AM14" s="84"/>
+      <c r="AN14" s="84"/>
+      <c r="AO14" s="84"/>
+      <c r="AP14" s="84"/>
+      <c r="AQ14" s="84"/>
+      <c r="AR14" s="84"/>
+      <c r="AS14" s="84"/>
+      <c r="AT14" s="84"/>
+      <c r="AU14" s="84"/>
+      <c r="AV14" s="84"/>
+      <c r="AW14" s="84"/>
+      <c r="AX14" s="84"/>
+      <c r="AY14" s="84"/>
+      <c r="AZ14" s="84"/>
+      <c r="BA14" s="84"/>
+      <c r="BB14" s="84"/>
+      <c r="BC14" s="84"/>
+      <c r="BD14" s="84"/>
+      <c r="BE14" s="84"/>
+      <c r="BF14" s="84"/>
+      <c r="BG14" s="84"/>
+      <c r="BH14" s="84"/>
+      <c r="BI14" s="84"/>
+      <c r="BJ14" s="84"/>
+      <c r="BK14" s="84"/>
+      <c r="BL14" s="84"/>
+      <c r="BM14" s="84"/>
+      <c r="BN14" s="84"/>
+      <c r="BO14" s="84"/>
+      <c r="BP14" s="84"/>
+      <c r="BQ14" s="84"/>
+      <c r="BR14" s="84"/>
+      <c r="BS14" s="84"/>
+      <c r="BT14" s="91"/>
+      <c r="BU14" s="90"/>
+      <c r="BV14" s="84"/>
+      <c r="BW14" s="84"/>
+      <c r="BX14" s="84"/>
+      <c r="BY14" s="84"/>
+      <c r="BZ14" s="84"/>
+      <c r="CA14" s="84"/>
+      <c r="CB14" s="84"/>
+      <c r="CC14" s="84"/>
+      <c r="CD14" s="84"/>
+      <c r="CE14" s="84"/>
+      <c r="CF14" s="84"/>
+      <c r="CG14" s="84"/>
+      <c r="CH14" s="84"/>
+      <c r="CI14" s="84"/>
+      <c r="CJ14" s="84"/>
+      <c r="CK14" s="84"/>
+      <c r="CL14" s="84"/>
+      <c r="CM14" s="84"/>
+      <c r="CN14" s="84"/>
+      <c r="CO14" s="90"/>
+      <c r="CP14" s="84"/>
+      <c r="CQ14" s="84"/>
+      <c r="CR14" s="84"/>
+      <c r="CS14" s="84"/>
+      <c r="CT14" s="84"/>
+      <c r="CU14" s="84"/>
+      <c r="CV14" s="84"/>
+      <c r="CW14" s="84"/>
+      <c r="CX14" s="91"/>
     </row>
-    <row r="15" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
+    <row r="15" spans="5:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
       <c r="H15" s="16"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -2931,10 +2939,10 @@
       <c r="CW15" s="24"/>
       <c r="CX15" s="25"/>
     </row>
-    <row r="16" spans="5:102" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
+    <row r="16" spans="5:102" ht="96.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
@@ -3031,10 +3039,10 @@
       <c r="CW16" s="33"/>
       <c r="CX16" s="34"/>
     </row>
-    <row r="17" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
+    <row r="17" spans="1:102" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
       <c r="J17" s="36"/>
@@ -3131,7 +3139,7 @@
       <c r="CW17" s="43"/>
       <c r="CX17" s="44"/>
     </row>
-    <row r="18" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:102" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="45"/>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -3143,7 +3151,7 @@
         <v>2301102644</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="50"/>
       <c r="I18" s="48"/>
@@ -3241,16 +3249,16 @@
       <c r="CW18" s="54"/>
       <c r="CX18" s="55"/>
     </row>
-    <row r="19" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:102" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="56"/>
       <c r="E19" s="57">
         <v>2</v>
       </c>
-      <c r="F19" s="58">
-        <v>2301100000</v>
+      <c r="F19" s="70">
+        <v>10</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="60"/>
       <c r="I19" s="61"/>
@@ -3348,16 +3356,16 @@
       <c r="CW19" s="67"/>
       <c r="CX19" s="68"/>
     </row>
-    <row r="20" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:102" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="56"/>
       <c r="E20" s="57">
         <v>3</v>
       </c>
-      <c r="F20" s="58">
-        <v>2001102089</v>
+      <c r="F20" s="70">
+        <v>11</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
@@ -3455,16 +3463,16 @@
       <c r="CW20" s="67"/>
       <c r="CX20" s="68"/>
     </row>
-    <row r="21" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="56"/>
       <c r="E21" s="57">
         <v>4</v>
       </c>
-      <c r="F21" s="58">
-        <v>2201105829</v>
+      <c r="F21" s="70">
+        <v>12</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
@@ -3562,16 +3570,16 @@
       <c r="CW21" s="67"/>
       <c r="CX21" s="68"/>
     </row>
-    <row r="22" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="56"/>
       <c r="E22" s="57">
         <v>5</v>
       </c>
-      <c r="F22" s="58">
-        <v>2201103056</v>
+      <c r="F22" s="70">
+        <v>13</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="60"/>
       <c r="I22" s="61"/>
@@ -3669,16 +3677,16 @@
       <c r="CW22" s="67"/>
       <c r="CX22" s="68"/>
     </row>
-    <row r="23" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
       <c r="E23" s="57">
         <v>6</v>
       </c>
-      <c r="F23" s="58">
-        <v>2201100446</v>
+      <c r="F23" s="70">
+        <v>14</v>
       </c>
       <c r="G23" s="59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
@@ -3776,16 +3784,16 @@
       <c r="CW23" s="67"/>
       <c r="CX23" s="68"/>
     </row>
-    <row r="24" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="56"/>
       <c r="E24" s="57">
         <v>7</v>
       </c>
-      <c r="F24" s="58">
-        <v>1801101449</v>
+      <c r="F24" s="70">
+        <v>15</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
@@ -3883,16 +3891,16 @@
       <c r="CW24" s="67"/>
       <c r="CX24" s="68"/>
     </row>
-    <row r="25" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="56"/>
       <c r="E25" s="57">
         <v>8</v>
       </c>
-      <c r="F25" s="58">
-        <v>2201104090</v>
+      <c r="F25" s="70">
+        <v>16</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H25" s="60"/>
       <c r="I25" s="61"/>
@@ -3990,16 +3998,16 @@
       <c r="CW25" s="67"/>
       <c r="CX25" s="68"/>
     </row>
-    <row r="26" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="56"/>
       <c r="E26" s="57">
         <v>9</v>
       </c>
-      <c r="F26" s="58">
-        <v>2201100596</v>
+      <c r="F26" s="70">
+        <v>17</v>
       </c>
       <c r="G26" s="59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
@@ -4097,16 +4105,16 @@
       <c r="CW26" s="67"/>
       <c r="CX26" s="68"/>
     </row>
-    <row r="27" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="56"/>
       <c r="E27" s="57">
         <v>10</v>
       </c>
-      <c r="F27" s="58">
-        <v>1801104290</v>
+      <c r="F27" s="70">
+        <v>18</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
@@ -4204,16 +4212,16 @@
       <c r="CW27" s="67"/>
       <c r="CX27" s="68"/>
     </row>
-    <row r="28" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="56"/>
       <c r="E28" s="57">
         <v>11</v>
       </c>
-      <c r="F28" s="58">
-        <v>2201104808</v>
+      <c r="F28" s="70">
+        <v>19</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H28" s="60"/>
       <c r="I28" s="61"/>
@@ -4311,16 +4319,16 @@
       <c r="CW28" s="67"/>
       <c r="CX28" s="68"/>
     </row>
-    <row r="29" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="56"/>
       <c r="E29" s="57">
         <v>12</v>
       </c>
-      <c r="F29" s="58">
-        <v>1801102006</v>
+      <c r="F29" s="70">
+        <v>20</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H29" s="64"/>
       <c r="I29" s="58"/>
@@ -4418,16 +4426,16 @@
       <c r="CW29" s="67"/>
       <c r="CX29" s="68"/>
     </row>
-    <row r="30" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="56"/>
       <c r="E30" s="57">
         <v>13</v>
       </c>
-      <c r="F30" s="58">
-        <v>2201104863</v>
+      <c r="F30" s="70">
+        <v>21</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="64"/>
       <c r="I30" s="58"/>
@@ -4525,16 +4533,16 @@
       <c r="CW30" s="67"/>
       <c r="CX30" s="68"/>
     </row>
-    <row r="31" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="56"/>
       <c r="E31" s="57">
         <v>14</v>
       </c>
-      <c r="F31" s="58">
-        <v>2001103502</v>
+      <c r="F31" s="70">
+        <v>22</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H31" s="60"/>
       <c r="I31" s="61"/>
@@ -4632,16 +4640,16 @@
       <c r="CW31" s="67"/>
       <c r="CX31" s="68"/>
     </row>
-    <row r="32" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="56"/>
       <c r="E32" s="57">
         <v>15</v>
       </c>
-      <c r="F32" s="58">
-        <v>2201101446</v>
+      <c r="F32" s="70">
+        <v>23</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H32" s="64"/>
       <c r="I32" s="58"/>
@@ -4739,16 +4747,16 @@
       <c r="CW32" s="67"/>
       <c r="CX32" s="68"/>
     </row>
-    <row r="33" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="56"/>
       <c r="E33" s="57">
         <v>16</v>
       </c>
-      <c r="F33" s="58">
-        <v>2201101849</v>
+      <c r="F33" s="70">
+        <v>24</v>
       </c>
       <c r="G33" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H33" s="64"/>
       <c r="I33" s="58"/>
@@ -4846,16 +4854,16 @@
       <c r="CW33" s="67"/>
       <c r="CX33" s="68"/>
     </row>
-    <row r="34" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="56"/>
       <c r="E34" s="57">
         <v>17</v>
       </c>
-      <c r="F34" s="58">
-        <v>2201105671</v>
+      <c r="F34" s="70">
+        <v>25</v>
       </c>
       <c r="G34" s="59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H34" s="60"/>
       <c r="I34" s="61"/>
@@ -4953,16 +4961,16 @@
       <c r="CW34" s="67"/>
       <c r="CX34" s="68"/>
     </row>
-    <row r="35" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="56"/>
       <c r="E35" s="57">
         <v>18</v>
       </c>
-      <c r="F35" s="58">
-        <v>2201110117</v>
+      <c r="F35" s="70">
+        <v>26</v>
       </c>
       <c r="G35" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H35" s="64"/>
       <c r="I35" s="58"/>
@@ -5060,16 +5068,16 @@
       <c r="CW35" s="67"/>
       <c r="CX35" s="68"/>
     </row>
-    <row r="36" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="56"/>
       <c r="E36" s="57">
         <v>19</v>
       </c>
-      <c r="F36" s="58">
-        <v>2201102197</v>
+      <c r="F36" s="70">
+        <v>27</v>
       </c>
       <c r="G36" s="59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H36" s="64"/>
       <c r="I36" s="58"/>
@@ -5167,16 +5175,16 @@
       <c r="CW36" s="67"/>
       <c r="CX36" s="68"/>
     </row>
-    <row r="37" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="56"/>
       <c r="E37" s="57">
         <v>20</v>
       </c>
-      <c r="F37" s="58">
-        <v>2201104861</v>
+      <c r="F37" s="70">
+        <v>28</v>
       </c>
       <c r="G37" s="59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H37" s="60"/>
       <c r="I37" s="61"/>
@@ -5274,16 +5282,16 @@
       <c r="CW37" s="67"/>
       <c r="CX37" s="68"/>
     </row>
-    <row r="38" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="56"/>
       <c r="E38" s="57">
         <v>21</v>
       </c>
-      <c r="F38" s="58">
-        <v>2201106018</v>
+      <c r="F38" s="70">
+        <v>29</v>
       </c>
       <c r="G38" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H38" s="64"/>
       <c r="I38" s="58"/>
@@ -5381,16 +5389,16 @@
       <c r="CW38" s="67"/>
       <c r="CX38" s="68"/>
     </row>
-    <row r="39" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="56"/>
       <c r="E39" s="57">
         <v>22</v>
       </c>
-      <c r="F39" s="58">
-        <v>2201100405</v>
+      <c r="F39" s="70">
+        <v>30</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H39" s="64"/>
       <c r="I39" s="58"/>
@@ -5488,16 +5496,16 @@
       <c r="CW39" s="67"/>
       <c r="CX39" s="68"/>
     </row>
-    <row r="40" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="56"/>
       <c r="E40" s="57">
         <v>23</v>
       </c>
-      <c r="F40" s="58">
-        <v>2201108251</v>
+      <c r="F40" s="70">
+        <v>31</v>
       </c>
       <c r="G40" s="59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H40" s="60"/>
       <c r="I40" s="61"/>
@@ -5595,7 +5603,7 @@
       <c r="CW40" s="67"/>
       <c r="CX40" s="68"/>
     </row>
-    <row r="41" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="56"/>
       <c r="E41" s="57">
         <v>24</v>
@@ -5698,7 +5706,7 @@
       <c r="CW41" s="67"/>
       <c r="CX41" s="68"/>
     </row>
-    <row r="42" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="56"/>
       <c r="E42" s="57">
         <v>25</v>
@@ -5801,7 +5809,7 @@
       <c r="CW42" s="67"/>
       <c r="CX42" s="68"/>
     </row>
-    <row r="43" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="56"/>
       <c r="E43" s="57">
         <v>26</v>
@@ -5904,7 +5912,7 @@
       <c r="CW43" s="67"/>
       <c r="CX43" s="68"/>
     </row>
-    <row r="44" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="56"/>
       <c r="E44" s="57">
         <v>27</v>
@@ -6007,7 +6015,7 @@
       <c r="CW44" s="67"/>
       <c r="CX44" s="68"/>
     </row>
-    <row r="45" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="56"/>
       <c r="E45" s="57">
         <v>28</v>
@@ -6110,7 +6118,7 @@
       <c r="CW45" s="67"/>
       <c r="CX45" s="68"/>
     </row>
-    <row r="46" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="56"/>
       <c r="E46" s="57">
         <v>29</v>
@@ -6213,7 +6221,7 @@
       <c r="CW46" s="67"/>
       <c r="CX46" s="68"/>
     </row>
-    <row r="47" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="56"/>
       <c r="E47" s="57">
         <v>30</v>
@@ -6316,7 +6324,7 @@
       <c r="CW47" s="67"/>
       <c r="CX47" s="68"/>
     </row>
-    <row r="48" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="56"/>
       <c r="E48" s="57">
         <v>31</v>
@@ -6419,7 +6427,7 @@
       <c r="CW48" s="67"/>
       <c r="CX48" s="68"/>
     </row>
-    <row r="49" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="56"/>
       <c r="E49" s="57">
         <v>32</v>
@@ -6522,7 +6530,7 @@
       <c r="CW49" s="67"/>
       <c r="CX49" s="68"/>
     </row>
-    <row r="50" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="56"/>
       <c r="E50" s="57">
         <v>33</v>
@@ -6625,7 +6633,7 @@
       <c r="CW50" s="67"/>
       <c r="CX50" s="68"/>
     </row>
-    <row r="51" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="56"/>
       <c r="E51" s="57">
         <v>34</v>
@@ -6728,7 +6736,7 @@
       <c r="CW51" s="67"/>
       <c r="CX51" s="68"/>
     </row>
-    <row r="52" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="56"/>
       <c r="E52" s="57">
         <v>35</v>
@@ -6831,7 +6839,7 @@
       <c r="CW52" s="67"/>
       <c r="CX52" s="68"/>
     </row>
-    <row r="53" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="56"/>
       <c r="E53" s="57">
         <v>36</v>
@@ -6934,7 +6942,7 @@
       <c r="CW53" s="67"/>
       <c r="CX53" s="68"/>
     </row>
-    <row r="54" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="56"/>
       <c r="E54" s="57">
         <v>37</v>
@@ -7037,7 +7045,7 @@
       <c r="CW54" s="67"/>
       <c r="CX54" s="68"/>
     </row>
-    <row r="55" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="56"/>
       <c r="E55" s="57">
         <v>38</v>
@@ -7140,7 +7148,7 @@
       <c r="CW55" s="67"/>
       <c r="CX55" s="68"/>
     </row>
-    <row r="56" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="56"/>
       <c r="E56" s="57">
         <v>39</v>
@@ -7243,7 +7251,7 @@
       <c r="CW56" s="67"/>
       <c r="CX56" s="68"/>
     </row>
-    <row r="57" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="56"/>
       <c r="E57" s="57">
         <v>40</v>
@@ -7346,7 +7354,7 @@
       <c r="CW57" s="67"/>
       <c r="CX57" s="68"/>
     </row>
-    <row r="58" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="56"/>
       <c r="E58" s="57">
         <v>41</v>
@@ -7449,7 +7457,7 @@
       <c r="CW58" s="67"/>
       <c r="CX58" s="68"/>
     </row>
-    <row r="59" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="56"/>
       <c r="E59" s="57">
         <v>42</v>
@@ -7552,7 +7560,7 @@
       <c r="CW59" s="67"/>
       <c r="CX59" s="68"/>
     </row>
-    <row r="60" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="56"/>
       <c r="E60" s="57">
         <v>43</v>
@@ -7655,7 +7663,7 @@
       <c r="CW60" s="67"/>
       <c r="CX60" s="68"/>
     </row>
-    <row r="61" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="56"/>
       <c r="E61" s="57">
         <v>44</v>
@@ -7758,7 +7766,7 @@
       <c r="CW61" s="67"/>
       <c r="CX61" s="68"/>
     </row>
-    <row r="62" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="56"/>
       <c r="E62" s="57">
         <v>45</v>
@@ -7861,7 +7869,7 @@
       <c r="CW62" s="67"/>
       <c r="CX62" s="68"/>
     </row>
-    <row r="63" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="56"/>
       <c r="E63" s="57">
         <v>46</v>
@@ -7964,7 +7972,7 @@
       <c r="CW63" s="67"/>
       <c r="CX63" s="68"/>
     </row>
-    <row r="64" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="56"/>
       <c r="E64" s="57">
         <v>47</v>
@@ -8067,7 +8075,7 @@
       <c r="CW64" s="67"/>
       <c r="CX64" s="68"/>
     </row>
-    <row r="65" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="56"/>
       <c r="E65" s="57">
         <v>48</v>
@@ -8170,7 +8178,7 @@
       <c r="CW65" s="67"/>
       <c r="CX65" s="68"/>
     </row>
-    <row r="66" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="56"/>
       <c r="E66" s="57">
         <v>49</v>
@@ -8273,7 +8281,7 @@
       <c r="CW66" s="67"/>
       <c r="CX66" s="68"/>
     </row>
-    <row r="67" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="56"/>
       <c r="E67" s="57">
         <v>50</v>
@@ -8376,7 +8384,7 @@
       <c r="CW67" s="67"/>
       <c r="CX67" s="68"/>
     </row>
-    <row r="68" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="56"/>
       <c r="E68" s="57">
         <v>51</v>
@@ -8479,7 +8487,7 @@
       <c r="CW68" s="67"/>
       <c r="CX68" s="68"/>
     </row>
-    <row r="69" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="56"/>
       <c r="E69" s="57">
         <v>52</v>
@@ -8582,7 +8590,7 @@
       <c r="CW69" s="67"/>
       <c r="CX69" s="68"/>
     </row>
-    <row r="70" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="56"/>
       <c r="E70" s="57">
         <v>53</v>
@@ -8685,7 +8693,7 @@
       <c r="CW70" s="67"/>
       <c r="CX70" s="68"/>
     </row>
-    <row r="71" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="56"/>
       <c r="E71" s="57">
         <v>54</v>
@@ -8788,7 +8796,7 @@
       <c r="CW71" s="67"/>
       <c r="CX71" s="68"/>
     </row>
-    <row r="72" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="56"/>
       <c r="E72" s="57">
         <v>55</v>
@@ -8891,7 +8899,7 @@
       <c r="CW72" s="67"/>
       <c r="CX72" s="68"/>
     </row>
-    <row r="73" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="56"/>
       <c r="E73" s="57">
         <v>56</v>
@@ -8994,7 +9002,7 @@
       <c r="CW73" s="67"/>
       <c r="CX73" s="68"/>
     </row>
-    <row r="74" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="56"/>
       <c r="E74" s="57">
         <v>57</v>
@@ -9097,7 +9105,7 @@
       <c r="CW74" s="67"/>
       <c r="CX74" s="68"/>
     </row>
-    <row r="75" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="56"/>
       <c r="E75" s="57">
         <v>58</v>
@@ -9200,7 +9208,7 @@
       <c r="CW75" s="67"/>
       <c r="CX75" s="68"/>
     </row>
-    <row r="76" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="56"/>
       <c r="E76" s="57">
         <v>59</v>
@@ -9303,7 +9311,7 @@
       <c r="CW76" s="67"/>
       <c r="CX76" s="68"/>
     </row>
-    <row r="77" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="56"/>
       <c r="E77" s="57">
         <v>60</v>
@@ -9406,7 +9414,7 @@
       <c r="CW77" s="67"/>
       <c r="CX77" s="68"/>
     </row>
-    <row r="78" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="56"/>
       <c r="E78" s="57">
         <v>61</v>
@@ -9509,7 +9517,7 @@
       <c r="CW78" s="67"/>
       <c r="CX78" s="68"/>
     </row>
-    <row r="79" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="56"/>
       <c r="E79" s="57">
         <v>62</v>
@@ -9612,7 +9620,7 @@
       <c r="CW79" s="67"/>
       <c r="CX79" s="68"/>
     </row>
-    <row r="80" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="56"/>
       <c r="E80" s="57">
         <v>63</v>
@@ -9715,7 +9723,7 @@
       <c r="CW80" s="67"/>
       <c r="CX80" s="68"/>
     </row>
-    <row r="81" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="56"/>
       <c r="E81" s="57">
         <v>64</v>
@@ -9818,7 +9826,7 @@
       <c r="CW81" s="67"/>
       <c r="CX81" s="68"/>
     </row>
-    <row r="82" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="56"/>
       <c r="E82" s="57">
         <v>65</v>
@@ -9921,7 +9929,7 @@
       <c r="CW82" s="67"/>
       <c r="CX82" s="68"/>
     </row>
-    <row r="83" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="56"/>
       <c r="E83" s="57">
         <v>66</v>
@@ -10024,7 +10032,7 @@
       <c r="CW83" s="67"/>
       <c r="CX83" s="68"/>
     </row>
-    <row r="84" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="56"/>
       <c r="E84" s="57">
         <v>67</v>
@@ -10127,7 +10135,7 @@
       <c r="CW84" s="67"/>
       <c r="CX84" s="68"/>
     </row>
-    <row r="85" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="56"/>
       <c r="E85" s="57">
         <v>68</v>
@@ -10230,7 +10238,7 @@
       <c r="CW85" s="67"/>
       <c r="CX85" s="68"/>
     </row>
-    <row r="86" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="56"/>
       <c r="E86" s="57">
         <v>69</v>
@@ -10333,7 +10341,7 @@
       <c r="CW86" s="67"/>
       <c r="CX86" s="68"/>
     </row>
-    <row r="87" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="69"/>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -10439,7 +10447,7 @@
       <c r="CW87" s="67"/>
       <c r="CX87" s="68"/>
     </row>
-    <row r="88" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:102" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E88" s="57">
         <v>71</v>
       </c>
@@ -10541,7 +10549,7 @@
       <c r="CW88" s="67"/>
       <c r="CX88" s="68"/>
     </row>
-    <row r="89" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E89" s="57">
         <v>72</v>
       </c>
@@ -10643,7 +10651,7 @@
       <c r="CW89" s="67"/>
       <c r="CX89" s="68"/>
     </row>
-    <row r="90" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E90" s="57">
         <v>73</v>
       </c>
@@ -10745,7 +10753,7 @@
       <c r="CW90" s="67"/>
       <c r="CX90" s="68"/>
     </row>
-    <row r="91" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E91" s="57">
         <v>74</v>
       </c>
@@ -10847,7 +10855,7 @@
       <c r="CW91" s="67"/>
       <c r="CX91" s="68"/>
     </row>
-    <row r="92" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E92" s="57">
         <v>75</v>
       </c>
@@ -10949,7 +10957,7 @@
       <c r="CW92" s="67"/>
       <c r="CX92" s="68"/>
     </row>
-    <row r="93" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E93" s="57">
         <v>76</v>
       </c>
@@ -11051,7 +11059,7 @@
       <c r="CW93" s="67"/>
       <c r="CX93" s="68"/>
     </row>
-    <row r="94" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E94" s="57">
         <v>77</v>
       </c>
@@ -11153,7 +11161,7 @@
       <c r="CW94" s="67"/>
       <c r="CX94" s="68"/>
     </row>
-    <row r="95" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E95" s="57">
         <v>78</v>
       </c>
@@ -11255,7 +11263,7 @@
       <c r="CW95" s="67"/>
       <c r="CX95" s="68"/>
     </row>
-    <row r="96" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E96" s="57">
         <v>79</v>
       </c>
@@ -11357,7 +11365,7 @@
       <c r="CW96" s="67"/>
       <c r="CX96" s="68"/>
     </row>
-    <row r="97" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E97" s="57">
         <v>80</v>
       </c>
@@ -11459,7 +11467,7 @@
       <c r="CW97" s="67"/>
       <c r="CX97" s="68"/>
     </row>
-    <row r="98" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E98" s="57">
         <v>81</v>
       </c>
@@ -11561,7 +11569,7 @@
       <c r="CW98" s="67"/>
       <c r="CX98" s="68"/>
     </row>
-    <row r="99" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E99" s="57">
         <v>82</v>
       </c>
@@ -11663,7 +11671,7 @@
       <c r="CW99" s="67"/>
       <c r="CX99" s="68"/>
     </row>
-    <row r="100" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E100" s="57">
         <v>83</v>
       </c>
@@ -11765,7 +11773,7 @@
       <c r="CW100" s="67"/>
       <c r="CX100" s="68"/>
     </row>
-    <row r="101" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E101" s="57">
         <v>84</v>
       </c>
@@ -11867,7 +11875,7 @@
       <c r="CW101" s="67"/>
       <c r="CX101" s="68"/>
     </row>
-    <row r="102" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E102" s="57">
         <v>85</v>
       </c>
@@ -11969,7 +11977,7 @@
       <c r="CW102" s="67"/>
       <c r="CX102" s="68"/>
     </row>
-    <row r="103" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E103" s="57">
         <v>86</v>
       </c>
@@ -12071,7 +12079,7 @@
       <c r="CW103" s="67"/>
       <c r="CX103" s="68"/>
     </row>
-    <row r="104" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E104" s="57">
         <v>87</v>
       </c>
@@ -12173,7 +12181,7 @@
       <c r="CW104" s="67"/>
       <c r="CX104" s="68"/>
     </row>
-    <row r="105" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E105" s="57">
         <v>88</v>
       </c>
@@ -12275,7 +12283,7 @@
       <c r="CW105" s="67"/>
       <c r="CX105" s="68"/>
     </row>
-    <row r="106" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E106" s="57">
         <v>89</v>
       </c>
@@ -12377,7 +12385,7 @@
       <c r="CW106" s="67"/>
       <c r="CX106" s="68"/>
     </row>
-    <row r="107" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E107" s="57">
         <v>90</v>
       </c>
@@ -12479,7 +12487,7 @@
       <c r="CW107" s="67"/>
       <c r="CX107" s="68"/>
     </row>
-    <row r="108" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E108" s="57">
         <v>91</v>
       </c>
@@ -12581,7 +12589,7 @@
       <c r="CW108" s="67"/>
       <c r="CX108" s="68"/>
     </row>
-    <row r="109" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E109" s="57">
         <v>92</v>
       </c>
@@ -12683,7 +12691,7 @@
       <c r="CW109" s="67"/>
       <c r="CX109" s="68"/>
     </row>
-    <row r="110" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E110" s="57">
         <v>93</v>
       </c>
@@ -12785,7 +12793,7 @@
       <c r="CW110" s="67"/>
       <c r="CX110" s="68"/>
     </row>
-    <row r="111" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E111" s="57">
         <v>94</v>
       </c>
@@ -12887,7 +12895,7 @@
       <c r="CW111" s="67"/>
       <c r="CX111" s="68"/>
     </row>
-    <row r="112" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E112" s="57">
         <v>95</v>
       </c>
@@ -12989,7 +12997,7 @@
       <c r="CW112" s="67"/>
       <c r="CX112" s="68"/>
     </row>
-    <row r="113" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E113" s="57">
         <v>96</v>
       </c>
@@ -13091,7 +13099,7 @@
       <c r="CW113" s="67"/>
       <c r="CX113" s="68"/>
     </row>
-    <row r="114" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E114" s="57">
         <v>97</v>
       </c>
@@ -13193,7 +13201,7 @@
       <c r="CW114" s="67"/>
       <c r="CX114" s="68"/>
     </row>
-    <row r="115" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E115" s="57">
         <v>98</v>
       </c>
@@ -13295,7 +13303,7 @@
       <c r="CW115" s="67"/>
       <c r="CX115" s="68"/>
     </row>
-    <row r="116" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E116" s="57">
         <v>99</v>
       </c>
@@ -13397,7 +13405,7 @@
       <c r="CW116" s="67"/>
       <c r="CX116" s="68"/>
     </row>
-    <row r="117" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:102" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E117" s="57">
         <v>100</v>
       </c>
@@ -13499,7 +13507,7 @@
       <c r="CW117" s="67"/>
       <c r="CX117" s="68"/>
     </row>
-    <row r="118" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
@@ -13596,7 +13604,7 @@
       <c r="CW118" s="2"/>
       <c r="CX118" s="2"/>
     </row>
-    <row r="119" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
@@ -13693,7 +13701,7 @@
       <c r="CW119" s="2"/>
       <c r="CX119" s="2"/>
     </row>
-    <row r="120" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
@@ -13790,7 +13798,7 @@
       <c r="CW120" s="2"/>
       <c r="CX120" s="2"/>
     </row>
-    <row r="121" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
@@ -13887,7 +13895,7 @@
       <c r="CW121" s="2"/>
       <c r="CX121" s="2"/>
     </row>
-    <row r="122" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
@@ -13984,7 +13992,7 @@
       <c r="CW122" s="2"/>
       <c r="CX122" s="2"/>
     </row>
-    <row r="123" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
@@ -14081,7 +14089,7 @@
       <c r="CW123" s="2"/>
       <c r="CX123" s="2"/>
     </row>
-    <row r="124" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
@@ -14178,7 +14186,7 @@
       <c r="CW124" s="2"/>
       <c r="CX124" s="2"/>
     </row>
-    <row r="125" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
@@ -14275,7 +14283,7 @@
       <c r="CW125" s="2"/>
       <c r="CX125" s="2"/>
     </row>
-    <row r="126" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
@@ -14372,7 +14380,7 @@
       <c r="CW126" s="2"/>
       <c r="CX126" s="2"/>
     </row>
-    <row r="127" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
@@ -14469,7 +14477,7 @@
       <c r="CW127" s="2"/>
       <c r="CX127" s="2"/>
     </row>
-    <row r="128" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
@@ -14566,7 +14574,7 @@
       <c r="CW128" s="2"/>
       <c r="CX128" s="2"/>
     </row>
-    <row r="129" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
@@ -14663,7 +14671,7 @@
       <c r="CW129" s="2"/>
       <c r="CX129" s="2"/>
     </row>
-    <row r="130" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
@@ -14760,7 +14768,7 @@
       <c r="CW130" s="2"/>
       <c r="CX130" s="2"/>
     </row>
-    <row r="131" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
@@ -14857,7 +14865,7 @@
       <c r="CW131" s="2"/>
       <c r="CX131" s="2"/>
     </row>
-    <row r="132" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
@@ -14954,7 +14962,7 @@
       <c r="CW132" s="2"/>
       <c r="CX132" s="2"/>
     </row>
-    <row r="133" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
@@ -15051,7 +15059,7 @@
       <c r="CW133" s="2"/>
       <c r="CX133" s="2"/>
     </row>
-    <row r="134" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
@@ -15148,7 +15156,7 @@
       <c r="CW134" s="2"/>
       <c r="CX134" s="2"/>
     </row>
-    <row r="135" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
@@ -15245,7 +15253,7 @@
       <c r="CW135" s="2"/>
       <c r="CX135" s="2"/>
     </row>
-    <row r="136" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
@@ -15342,7 +15350,7 @@
       <c r="CW136" s="2"/>
       <c r="CX136" s="2"/>
     </row>
-    <row r="137" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
@@ -15439,7 +15447,7 @@
       <c r="CW137" s="2"/>
       <c r="CX137" s="2"/>
     </row>
-    <row r="138" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
@@ -15536,7 +15544,7 @@
       <c r="CW138" s="2"/>
       <c r="CX138" s="2"/>
     </row>
-    <row r="139" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
@@ -15633,7 +15641,7 @@
       <c r="CW139" s="2"/>
       <c r="CX139" s="2"/>
     </row>
-    <row r="140" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
@@ -15730,7 +15738,7 @@
       <c r="CW140" s="2"/>
       <c r="CX140" s="2"/>
     </row>
-    <row r="141" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
@@ -15827,7 +15835,7 @@
       <c r="CW141" s="2"/>
       <c r="CX141" s="2"/>
     </row>
-    <row r="142" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
@@ -15924,7 +15932,7 @@
       <c r="CW142" s="2"/>
       <c r="CX142" s="2"/>
     </row>
-    <row r="143" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
@@ -16021,7 +16029,7 @@
       <c r="CW143" s="2"/>
       <c r="CX143" s="2"/>
     </row>
-    <row r="144" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
@@ -16118,7 +16126,7 @@
       <c r="CW144" s="2"/>
       <c r="CX144" s="2"/>
     </row>
-    <row r="145" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
@@ -16215,7 +16223,7 @@
       <c r="CW145" s="2"/>
       <c r="CX145" s="2"/>
     </row>
-    <row r="146" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
@@ -16312,7 +16320,7 @@
       <c r="CW146" s="2"/>
       <c r="CX146" s="2"/>
     </row>
-    <row r="147" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
@@ -16409,7 +16417,7 @@
       <c r="CW147" s="2"/>
       <c r="CX147" s="2"/>
     </row>
-    <row r="148" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
@@ -16506,7 +16514,7 @@
       <c r="CW148" s="2"/>
       <c r="CX148" s="2"/>
     </row>
-    <row r="149" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
@@ -16603,7 +16611,7 @@
       <c r="CW149" s="2"/>
       <c r="CX149" s="2"/>
     </row>
-    <row r="150" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
@@ -16700,7 +16708,7 @@
       <c r="CW150" s="2"/>
       <c r="CX150" s="2"/>
     </row>
-    <row r="151" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
@@ -16797,7 +16805,7 @@
       <c r="CW151" s="2"/>
       <c r="CX151" s="2"/>
     </row>
-    <row r="152" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
@@ -16894,7 +16902,7 @@
       <c r="CW152" s="2"/>
       <c r="CX152" s="2"/>
     </row>
-    <row r="153" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
@@ -16991,7 +16999,7 @@
       <c r="CW153" s="2"/>
       <c r="CX153" s="2"/>
     </row>
-    <row r="154" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
@@ -17088,7 +17096,7 @@
       <c r="CW154" s="2"/>
       <c r="CX154" s="2"/>
     </row>
-    <row r="155" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
@@ -17185,7 +17193,7 @@
       <c r="CW155" s="2"/>
       <c r="CX155" s="2"/>
     </row>
-    <row r="156" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
@@ -17282,7 +17290,7 @@
       <c r="CW156" s="2"/>
       <c r="CX156" s="2"/>
     </row>
-    <row r="157" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
@@ -17379,7 +17387,7 @@
       <c r="CW157" s="2"/>
       <c r="CX157" s="2"/>
     </row>
-    <row r="158" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
@@ -17476,7 +17484,7 @@
       <c r="CW158" s="2"/>
       <c r="CX158" s="2"/>
     </row>
-    <row r="159" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
@@ -17573,7 +17581,7 @@
       <c r="CW159" s="2"/>
       <c r="CX159" s="2"/>
     </row>
-    <row r="160" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
@@ -17670,7 +17678,7 @@
       <c r="CW160" s="2"/>
       <c r="CX160" s="2"/>
     </row>
-    <row r="161" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
@@ -17767,7 +17775,7 @@
       <c r="CW161" s="2"/>
       <c r="CX161" s="2"/>
     </row>
-    <row r="162" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
@@ -17864,7 +17872,7 @@
       <c r="CW162" s="2"/>
       <c r="CX162" s="2"/>
     </row>
-    <row r="163" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
@@ -17961,7 +17969,7 @@
       <c r="CW163" s="2"/>
       <c r="CX163" s="2"/>
     </row>
-    <row r="164" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
@@ -18058,7 +18066,7 @@
       <c r="CW164" s="2"/>
       <c r="CX164" s="2"/>
     </row>
-    <row r="165" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
@@ -18155,7 +18163,7 @@
       <c r="CW165" s="2"/>
       <c r="CX165" s="2"/>
     </row>
-    <row r="166" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
@@ -18252,7 +18260,7 @@
       <c r="CW166" s="2"/>
       <c r="CX166" s="2"/>
     </row>
-    <row r="167" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
@@ -18349,7 +18357,7 @@
       <c r="CW167" s="2"/>
       <c r="CX167" s="2"/>
     </row>
-    <row r="168" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
@@ -18446,7 +18454,7 @@
       <c r="CW168" s="2"/>
       <c r="CX168" s="2"/>
     </row>
-    <row r="169" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
@@ -18543,7 +18551,7 @@
       <c r="CW169" s="2"/>
       <c r="CX169" s="2"/>
     </row>
-    <row r="170" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
@@ -18640,7 +18648,7 @@
       <c r="CW170" s="2"/>
       <c r="CX170" s="2"/>
     </row>
-    <row r="171" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
@@ -18737,7 +18745,7 @@
       <c r="CW171" s="2"/>
       <c r="CX171" s="2"/>
     </row>
-    <row r="172" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
@@ -18834,7 +18842,7 @@
       <c r="CW172" s="2"/>
       <c r="CX172" s="2"/>
     </row>
-    <row r="173" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
@@ -18931,7 +18939,7 @@
       <c r="CW173" s="2"/>
       <c r="CX173" s="2"/>
     </row>
-    <row r="174" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
@@ -19028,7 +19036,7 @@
       <c r="CW174" s="2"/>
       <c r="CX174" s="2"/>
     </row>
-    <row r="175" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
@@ -19125,7 +19133,7 @@
       <c r="CW175" s="2"/>
       <c r="CX175" s="2"/>
     </row>
-    <row r="176" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
@@ -19222,7 +19230,7 @@
       <c r="CW176" s="2"/>
       <c r="CX176" s="2"/>
     </row>
-    <row r="177" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
@@ -19319,7 +19327,7 @@
       <c r="CW177" s="2"/>
       <c r="CX177" s="2"/>
     </row>
-    <row r="178" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
@@ -19416,7 +19424,7 @@
       <c r="CW178" s="2"/>
       <c r="CX178" s="2"/>
     </row>
-    <row r="179" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
@@ -19513,7 +19521,7 @@
       <c r="CW179" s="2"/>
       <c r="CX179" s="2"/>
     </row>
-    <row r="180" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
@@ -19610,7 +19618,7 @@
       <c r="CW180" s="2"/>
       <c r="CX180" s="2"/>
     </row>
-    <row r="181" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
@@ -19707,7 +19715,7 @@
       <c r="CW181" s="2"/>
       <c r="CX181" s="2"/>
     </row>
-    <row r="182" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
@@ -19804,7 +19812,7 @@
       <c r="CW182" s="2"/>
       <c r="CX182" s="2"/>
     </row>
-    <row r="183" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
@@ -19901,7 +19909,7 @@
       <c r="CW183" s="2"/>
       <c r="CX183" s="2"/>
     </row>
-    <row r="184" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
@@ -19998,7 +20006,7 @@
       <c r="CW184" s="2"/>
       <c r="CX184" s="2"/>
     </row>
-    <row r="185" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
@@ -20095,7 +20103,7 @@
       <c r="CW185" s="2"/>
       <c r="CX185" s="2"/>
     </row>
-    <row r="186" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
@@ -20192,7 +20200,7 @@
       <c r="CW186" s="2"/>
       <c r="CX186" s="2"/>
     </row>
-    <row r="187" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
@@ -20289,7 +20297,7 @@
       <c r="CW187" s="2"/>
       <c r="CX187" s="2"/>
     </row>
-    <row r="188" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
@@ -20386,7 +20394,7 @@
       <c r="CW188" s="2"/>
       <c r="CX188" s="2"/>
     </row>
-    <row r="189" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
@@ -20483,7 +20491,7 @@
       <c r="CW189" s="2"/>
       <c r="CX189" s="2"/>
     </row>
-    <row r="190" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
@@ -20580,7 +20588,7 @@
       <c r="CW190" s="2"/>
       <c r="CX190" s="2"/>
     </row>
-    <row r="191" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
@@ -20677,7 +20685,7 @@
       <c r="CW191" s="2"/>
       <c r="CX191" s="2"/>
     </row>
-    <row r="192" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
@@ -20774,7 +20782,7 @@
       <c r="CW192" s="2"/>
       <c r="CX192" s="2"/>
     </row>
-    <row r="193" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
@@ -20871,7 +20879,7 @@
       <c r="CW193" s="2"/>
       <c r="CX193" s="2"/>
     </row>
-    <row r="194" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
@@ -20968,7 +20976,7 @@
       <c r="CW194" s="2"/>
       <c r="CX194" s="2"/>
     </row>
-    <row r="195" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
@@ -21065,7 +21073,7 @@
       <c r="CW195" s="2"/>
       <c r="CX195" s="2"/>
     </row>
-    <row r="196" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
@@ -21162,7 +21170,7 @@
       <c r="CW196" s="2"/>
       <c r="CX196" s="2"/>
     </row>
-    <row r="197" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
@@ -21259,7 +21267,7 @@
       <c r="CW197" s="2"/>
       <c r="CX197" s="2"/>
     </row>
-    <row r="198" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
@@ -21356,7 +21364,7 @@
       <c r="CW198" s="2"/>
       <c r="CX198" s="2"/>
     </row>
-    <row r="199" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
@@ -21453,7 +21461,7 @@
       <c r="CW199" s="2"/>
       <c r="CX199" s="2"/>
     </row>
-    <row r="200" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
@@ -21550,7 +21558,7 @@
       <c r="CW200" s="2"/>
       <c r="CX200" s="2"/>
     </row>
-    <row r="201" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
@@ -21647,7 +21655,7 @@
       <c r="CW201" s="2"/>
       <c r="CX201" s="2"/>
     </row>
-    <row r="202" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
@@ -21744,7 +21752,7 @@
       <c r="CW202" s="2"/>
       <c r="CX202" s="2"/>
     </row>
-    <row r="203" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
@@ -21841,7 +21849,7 @@
       <c r="CW203" s="2"/>
       <c r="CX203" s="2"/>
     </row>
-    <row r="204" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
@@ -21938,7 +21946,7 @@
       <c r="CW204" s="2"/>
       <c r="CX204" s="2"/>
     </row>
-    <row r="205" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
       <c r="J205" s="2"/>
@@ -22035,7 +22043,7 @@
       <c r="CW205" s="2"/>
       <c r="CX205" s="2"/>
     </row>
-    <row r="206" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
@@ -22132,7 +22140,7 @@
       <c r="CW206" s="2"/>
       <c r="CX206" s="2"/>
     </row>
-    <row r="207" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
@@ -22229,7 +22237,7 @@
       <c r="CW207" s="2"/>
       <c r="CX207" s="2"/>
     </row>
-    <row r="208" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
       <c r="J208" s="2"/>
@@ -22326,7 +22334,7 @@
       <c r="CW208" s="2"/>
       <c r="CX208" s="2"/>
     </row>
-    <row r="209" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
       <c r="J209" s="2"/>
@@ -22423,7 +22431,7 @@
       <c r="CW209" s="2"/>
       <c r="CX209" s="2"/>
     </row>
-    <row r="210" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
       <c r="J210" s="2"/>
@@ -22520,7 +22528,7 @@
       <c r="CW210" s="2"/>
       <c r="CX210" s="2"/>
     </row>
-    <row r="211" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
@@ -22617,7 +22625,7 @@
       <c r="CW211" s="2"/>
       <c r="CX211" s="2"/>
     </row>
-    <row r="212" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
@@ -22714,7 +22722,7 @@
       <c r="CW212" s="2"/>
       <c r="CX212" s="2"/>
     </row>
-    <row r="213" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
@@ -22811,7 +22819,7 @@
       <c r="CW213" s="2"/>
       <c r="CX213" s="2"/>
     </row>
-    <row r="214" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
@@ -22908,7 +22916,7 @@
       <c r="CW214" s="2"/>
       <c r="CX214" s="2"/>
     </row>
-    <row r="215" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
       <c r="J215" s="2"/>
@@ -23005,7 +23013,7 @@
       <c r="CW215" s="2"/>
       <c r="CX215" s="2"/>
     </row>
-    <row r="216" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
@@ -23102,7 +23110,7 @@
       <c r="CW216" s="2"/>
       <c r="CX216" s="2"/>
     </row>
-    <row r="217" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
@@ -23199,7 +23207,7 @@
       <c r="CW217" s="2"/>
       <c r="CX217" s="2"/>
     </row>
-    <row r="218" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
@@ -23296,7 +23304,7 @@
       <c r="CW218" s="2"/>
       <c r="CX218" s="2"/>
     </row>
-    <row r="219" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
@@ -23393,7 +23401,7 @@
       <c r="CW219" s="2"/>
       <c r="CX219" s="2"/>
     </row>
-    <row r="220" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
@@ -23490,7 +23498,7 @@
       <c r="CW220" s="2"/>
       <c r="CX220" s="2"/>
     </row>
-    <row r="221" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
@@ -23587,7 +23595,7 @@
       <c r="CW221" s="2"/>
       <c r="CX221" s="2"/>
     </row>
-    <row r="222" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -23684,7 +23692,7 @@
       <c r="CW222" s="2"/>
       <c r="CX222" s="2"/>
     </row>
-    <row r="223" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
       <c r="J223" s="2"/>
@@ -23781,7 +23789,7 @@
       <c r="CW223" s="2"/>
       <c r="CX223" s="2"/>
     </row>
-    <row r="224" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
@@ -23878,7 +23886,7 @@
       <c r="CW224" s="2"/>
       <c r="CX224" s="2"/>
     </row>
-    <row r="225" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
@@ -23975,7 +23983,7 @@
       <c r="CW225" s="2"/>
       <c r="CX225" s="2"/>
     </row>
-    <row r="226" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
@@ -24072,7 +24080,7 @@
       <c r="CW226" s="2"/>
       <c r="CX226" s="2"/>
     </row>
-    <row r="227" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
@@ -24169,7 +24177,7 @@
       <c r="CW227" s="2"/>
       <c r="CX227" s="2"/>
     </row>
-    <row r="228" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
@@ -24266,7 +24274,7 @@
       <c r="CW228" s="2"/>
       <c r="CX228" s="2"/>
     </row>
-    <row r="229" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
@@ -24363,7 +24371,7 @@
       <c r="CW229" s="2"/>
       <c r="CX229" s="2"/>
     </row>
-    <row r="230" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
@@ -24460,7 +24468,7 @@
       <c r="CW230" s="2"/>
       <c r="CX230" s="2"/>
     </row>
-    <row r="231" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
       <c r="J231" s="2"/>
@@ -24557,7 +24565,7 @@
       <c r="CW231" s="2"/>
       <c r="CX231" s="2"/>
     </row>
-    <row r="232" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
@@ -24654,7 +24662,7 @@
       <c r="CW232" s="2"/>
       <c r="CX232" s="2"/>
     </row>
-    <row r="233" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
@@ -24751,7 +24759,7 @@
       <c r="CW233" s="2"/>
       <c r="CX233" s="2"/>
     </row>
-    <row r="234" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
@@ -24848,7 +24856,7 @@
       <c r="CW234" s="2"/>
       <c r="CX234" s="2"/>
     </row>
-    <row r="235" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
@@ -24945,7 +24953,7 @@
       <c r="CW235" s="2"/>
       <c r="CX235" s="2"/>
     </row>
-    <row r="236" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -25042,7 +25050,7 @@
       <c r="CW236" s="2"/>
       <c r="CX236" s="2"/>
     </row>
-    <row r="237" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
@@ -25139,7 +25147,7 @@
       <c r="CW237" s="2"/>
       <c r="CX237" s="2"/>
     </row>
-    <row r="238" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -25236,7 +25244,7 @@
       <c r="CW238" s="2"/>
       <c r="CX238" s="2"/>
     </row>
-    <row r="239" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
@@ -25333,7 +25341,7 @@
       <c r="CW239" s="2"/>
       <c r="CX239" s="2"/>
     </row>
-    <row r="240" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
@@ -25430,7 +25438,7 @@
       <c r="CW240" s="2"/>
       <c r="CX240" s="2"/>
     </row>
-    <row r="241" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
@@ -25527,7 +25535,7 @@
       <c r="CW241" s="2"/>
       <c r="CX241" s="2"/>
     </row>
-    <row r="242" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -25624,7 +25632,7 @@
       <c r="CW242" s="2"/>
       <c r="CX242" s="2"/>
     </row>
-    <row r="243" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
       <c r="J243" s="2"/>
@@ -25721,7 +25729,7 @@
       <c r="CW243" s="2"/>
       <c r="CX243" s="2"/>
     </row>
-    <row r="244" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
       <c r="J244" s="2"/>
@@ -25818,7 +25826,7 @@
       <c r="CW244" s="2"/>
       <c r="CX244" s="2"/>
     </row>
-    <row r="245" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
       <c r="J245" s="2"/>
@@ -25915,7 +25923,7 @@
       <c r="CW245" s="2"/>
       <c r="CX245" s="2"/>
     </row>
-    <row r="246" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
       <c r="J246" s="2"/>
@@ -26012,7 +26020,7 @@
       <c r="CW246" s="2"/>
       <c r="CX246" s="2"/>
     </row>
-    <row r="247" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
       <c r="J247" s="2"/>
@@ -26109,7 +26117,7 @@
       <c r="CW247" s="2"/>
       <c r="CX247" s="2"/>
     </row>
-    <row r="248" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
       <c r="J248" s="2"/>
@@ -26206,7 +26214,7 @@
       <c r="CW248" s="2"/>
       <c r="CX248" s="2"/>
     </row>
-    <row r="249" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
       <c r="J249" s="2"/>
@@ -26303,7 +26311,7 @@
       <c r="CW249" s="2"/>
       <c r="CX249" s="2"/>
     </row>
-    <row r="250" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
       <c r="J250" s="2"/>
@@ -26400,7 +26408,7 @@
       <c r="CW250" s="2"/>
       <c r="CX250" s="2"/>
     </row>
-    <row r="251" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
       <c r="J251" s="2"/>
@@ -26497,7 +26505,7 @@
       <c r="CW251" s="2"/>
       <c r="CX251" s="2"/>
     </row>
-    <row r="252" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
       <c r="J252" s="2"/>
@@ -26594,7 +26602,7 @@
       <c r="CW252" s="2"/>
       <c r="CX252" s="2"/>
     </row>
-    <row r="253" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
@@ -26691,7 +26699,7 @@
       <c r="CW253" s="2"/>
       <c r="CX253" s="2"/>
     </row>
-    <row r="254" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H254" s="2"/>
       <c r="I254" s="2"/>
       <c r="J254" s="2"/>
@@ -26788,7 +26796,7 @@
       <c r="CW254" s="2"/>
       <c r="CX254" s="2"/>
     </row>
-    <row r="255" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H255" s="2"/>
       <c r="I255" s="2"/>
       <c r="J255" s="2"/>
@@ -26885,7 +26893,7 @@
       <c r="CW255" s="2"/>
       <c r="CX255" s="2"/>
     </row>
-    <row r="256" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
       <c r="J256" s="2"/>
@@ -26982,7 +26990,7 @@
       <c r="CW256" s="2"/>
       <c r="CX256" s="2"/>
     </row>
-    <row r="257" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
       <c r="J257" s="2"/>
@@ -27079,7 +27087,7 @@
       <c r="CW257" s="2"/>
       <c r="CX257" s="2"/>
     </row>
-    <row r="258" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
       <c r="J258" s="2"/>
@@ -27176,7 +27184,7 @@
       <c r="CW258" s="2"/>
       <c r="CX258" s="2"/>
     </row>
-    <row r="259" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H259" s="2"/>
       <c r="I259" s="2"/>
       <c r="J259" s="2"/>
@@ -27273,7 +27281,7 @@
       <c r="CW259" s="2"/>
       <c r="CX259" s="2"/>
     </row>
-    <row r="260" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H260" s="2"/>
       <c r="I260" s="2"/>
       <c r="J260" s="2"/>
@@ -27370,7 +27378,7 @@
       <c r="CW260" s="2"/>
       <c r="CX260" s="2"/>
     </row>
-    <row r="261" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H261" s="2"/>
       <c r="I261" s="2"/>
       <c r="J261" s="2"/>
@@ -27467,7 +27475,7 @@
       <c r="CW261" s="2"/>
       <c r="CX261" s="2"/>
     </row>
-    <row r="262" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
       <c r="J262" s="2"/>
@@ -27564,7 +27572,7 @@
       <c r="CW262" s="2"/>
       <c r="CX262" s="2"/>
     </row>
-    <row r="263" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
@@ -27661,7 +27669,7 @@
       <c r="CW263" s="2"/>
       <c r="CX263" s="2"/>
     </row>
-    <row r="264" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
       <c r="J264" s="2"/>
@@ -27758,7 +27766,7 @@
       <c r="CW264" s="2"/>
       <c r="CX264" s="2"/>
     </row>
-    <row r="265" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
       <c r="J265" s="2"/>
@@ -27855,7 +27863,7 @@
       <c r="CW265" s="2"/>
       <c r="CX265" s="2"/>
     </row>
-    <row r="266" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H266" s="2"/>
       <c r="I266" s="2"/>
       <c r="J266" s="2"/>
@@ -27952,7 +27960,7 @@
       <c r="CW266" s="2"/>
       <c r="CX266" s="2"/>
     </row>
-    <row r="267" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
       <c r="J267" s="2"/>
@@ -28049,7 +28057,7 @@
       <c r="CW267" s="2"/>
       <c r="CX267" s="2"/>
     </row>
-    <row r="268" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
       <c r="J268" s="2"/>
@@ -28146,7 +28154,7 @@
       <c r="CW268" s="2"/>
       <c r="CX268" s="2"/>
     </row>
-    <row r="269" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
       <c r="J269" s="2"/>
@@ -28243,7 +28251,7 @@
       <c r="CW269" s="2"/>
       <c r="CX269" s="2"/>
     </row>
-    <row r="270" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
       <c r="J270" s="2"/>
@@ -28340,7 +28348,7 @@
       <c r="CW270" s="2"/>
       <c r="CX270" s="2"/>
     </row>
-    <row r="271" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
       <c r="J271" s="2"/>
@@ -28437,7 +28445,7 @@
       <c r="CW271" s="2"/>
       <c r="CX271" s="2"/>
     </row>
-    <row r="272" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
@@ -28534,7 +28542,7 @@
       <c r="CW272" s="2"/>
       <c r="CX272" s="2"/>
     </row>
-    <row r="273" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
       <c r="J273" s="2"/>
@@ -28631,7 +28639,7 @@
       <c r="CW273" s="2"/>
       <c r="CX273" s="2"/>
     </row>
-    <row r="274" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
       <c r="J274" s="2"/>
@@ -28728,7 +28736,7 @@
       <c r="CW274" s="2"/>
       <c r="CX274" s="2"/>
     </row>
-    <row r="275" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
       <c r="J275" s="2"/>
@@ -28825,7 +28833,7 @@
       <c r="CW275" s="2"/>
       <c r="CX275" s="2"/>
     </row>
-    <row r="276" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H276" s="2"/>
       <c r="I276" s="2"/>
       <c r="J276" s="2"/>
@@ -28922,7 +28930,7 @@
       <c r="CW276" s="2"/>
       <c r="CX276" s="2"/>
     </row>
-    <row r="277" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
       <c r="J277" s="2"/>
@@ -29019,7 +29027,7 @@
       <c r="CW277" s="2"/>
       <c r="CX277" s="2"/>
     </row>
-    <row r="278" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
       <c r="J278" s="2"/>
@@ -29116,7 +29124,7 @@
       <c r="CW278" s="2"/>
       <c r="CX278" s="2"/>
     </row>
-    <row r="279" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
       <c r="J279" s="2"/>
@@ -29213,7 +29221,7 @@
       <c r="CW279" s="2"/>
       <c r="CX279" s="2"/>
     </row>
-    <row r="280" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
@@ -29310,7 +29318,7 @@
       <c r="CW280" s="2"/>
       <c r="CX280" s="2"/>
     </row>
-    <row r="281" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
       <c r="J281" s="2"/>
@@ -29407,7 +29415,7 @@
       <c r="CW281" s="2"/>
       <c r="CX281" s="2"/>
     </row>
-    <row r="282" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
       <c r="J282" s="2"/>
@@ -29504,7 +29512,7 @@
       <c r="CW282" s="2"/>
       <c r="CX282" s="2"/>
     </row>
-    <row r="283" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
       <c r="J283" s="2"/>
@@ -29601,7 +29609,7 @@
       <c r="CW283" s="2"/>
       <c r="CX283" s="2"/>
     </row>
-    <row r="284" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
       <c r="J284" s="2"/>
@@ -29698,7 +29706,7 @@
       <c r="CW284" s="2"/>
       <c r="CX284" s="2"/>
     </row>
-    <row r="285" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
       <c r="J285" s="2"/>
@@ -29795,7 +29803,7 @@
       <c r="CW285" s="2"/>
       <c r="CX285" s="2"/>
     </row>
-    <row r="286" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
       <c r="J286" s="2"/>
@@ -29892,7 +29900,7 @@
       <c r="CW286" s="2"/>
       <c r="CX286" s="2"/>
     </row>
-    <row r="287" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
       <c r="J287" s="2"/>
@@ -29989,7 +29997,7 @@
       <c r="CW287" s="2"/>
       <c r="CX287" s="2"/>
     </row>
-    <row r="288" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
       <c r="J288" s="2"/>
@@ -30086,7 +30094,7 @@
       <c r="CW288" s="2"/>
       <c r="CX288" s="2"/>
     </row>
-    <row r="289" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
       <c r="J289" s="2"/>
@@ -30183,7 +30191,7 @@
       <c r="CW289" s="2"/>
       <c r="CX289" s="2"/>
     </row>
-    <row r="290" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
       <c r="J290" s="2"/>
@@ -30280,7 +30288,7 @@
       <c r="CW290" s="2"/>
       <c r="CX290" s="2"/>
     </row>
-    <row r="291" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
       <c r="J291" s="2"/>
@@ -30377,7 +30385,7 @@
       <c r="CW291" s="2"/>
       <c r="CX291" s="2"/>
     </row>
-    <row r="292" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
       <c r="J292" s="2"/>
@@ -30474,7 +30482,7 @@
       <c r="CW292" s="2"/>
       <c r="CX292" s="2"/>
     </row>
-    <row r="293" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
       <c r="J293" s="2"/>
@@ -30571,7 +30579,7 @@
       <c r="CW293" s="2"/>
       <c r="CX293" s="2"/>
     </row>
-    <row r="294" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
       <c r="J294" s="2"/>
@@ -30668,7 +30676,7 @@
       <c r="CW294" s="2"/>
       <c r="CX294" s="2"/>
     </row>
-    <row r="295" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
       <c r="J295" s="2"/>
@@ -30765,7 +30773,7 @@
       <c r="CW295" s="2"/>
       <c r="CX295" s="2"/>
     </row>
-    <row r="296" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2"/>
@@ -30862,7 +30870,7 @@
       <c r="CW296" s="2"/>
       <c r="CX296" s="2"/>
     </row>
-    <row r="297" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
@@ -30959,7 +30967,7 @@
       <c r="CW297" s="2"/>
       <c r="CX297" s="2"/>
     </row>
-    <row r="298" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
@@ -31056,7 +31064,7 @@
       <c r="CW298" s="2"/>
       <c r="CX298" s="2"/>
     </row>
-    <row r="299" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
@@ -31153,7 +31161,7 @@
       <c r="CW299" s="2"/>
       <c r="CX299" s="2"/>
     </row>
-    <row r="300" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
@@ -31250,7 +31258,7 @@
       <c r="CW300" s="2"/>
       <c r="CX300" s="2"/>
     </row>
-    <row r="301" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
@@ -31347,7 +31355,7 @@
       <c r="CW301" s="2"/>
       <c r="CX301" s="2"/>
     </row>
-    <row r="302" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
@@ -31444,7 +31452,7 @@
       <c r="CW302" s="2"/>
       <c r="CX302" s="2"/>
     </row>
-    <row r="303" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
@@ -31541,7 +31549,7 @@
       <c r="CW303" s="2"/>
       <c r="CX303" s="2"/>
     </row>
-    <row r="304" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
@@ -31638,7 +31646,7 @@
       <c r="CW304" s="2"/>
       <c r="CX304" s="2"/>
     </row>
-    <row r="305" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
@@ -31735,7 +31743,7 @@
       <c r="CW305" s="2"/>
       <c r="CX305" s="2"/>
     </row>
-    <row r="306" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
@@ -31832,7 +31840,7 @@
       <c r="CW306" s="2"/>
       <c r="CX306" s="2"/>
     </row>
-    <row r="307" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
@@ -31929,7 +31937,7 @@
       <c r="CW307" s="2"/>
       <c r="CX307" s="2"/>
     </row>
-    <row r="308" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
@@ -32026,7 +32034,7 @@
       <c r="CW308" s="2"/>
       <c r="CX308" s="2"/>
     </row>
-    <row r="309" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
@@ -32123,7 +32131,7 @@
       <c r="CW309" s="2"/>
       <c r="CX309" s="2"/>
     </row>
-    <row r="310" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
@@ -32220,7 +32228,7 @@
       <c r="CW310" s="2"/>
       <c r="CX310" s="2"/>
     </row>
-    <row r="311" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H311" s="2"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
@@ -32317,7 +32325,7 @@
       <c r="CW311" s="2"/>
       <c r="CX311" s="2"/>
     </row>
-    <row r="312" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
@@ -32414,7 +32422,7 @@
       <c r="CW312" s="2"/>
       <c r="CX312" s="2"/>
     </row>
-    <row r="313" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2"/>
@@ -32511,7 +32519,7 @@
       <c r="CW313" s="2"/>
       <c r="CX313" s="2"/>
     </row>
-    <row r="314" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2"/>
@@ -32608,7 +32616,7 @@
       <c r="CW314" s="2"/>
       <c r="CX314" s="2"/>
     </row>
-    <row r="315" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
       <c r="J315" s="2"/>
@@ -32705,7 +32713,7 @@
       <c r="CW315" s="2"/>
       <c r="CX315" s="2"/>
     </row>
-    <row r="316" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
       <c r="J316" s="2"/>
@@ -32802,7 +32810,7 @@
       <c r="CW316" s="2"/>
       <c r="CX316" s="2"/>
     </row>
-    <row r="317" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="8:102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
       <c r="J317" s="2"/>
@@ -32901,6 +32909,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="CO13:CX14"/>
+    <mergeCell ref="K11:O11"/>
+    <mergeCell ref="BU13:CN14"/>
+    <mergeCell ref="AC10:BP10"/>
+    <mergeCell ref="K9:O9"/>
+    <mergeCell ref="AB12:AD12"/>
+    <mergeCell ref="E2:CX2"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="V10:Z10"/>
+    <mergeCell ref="S7:W7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="AC8:BP8"/>
+    <mergeCell ref="E3:CX3"/>
+    <mergeCell ref="AC7:BP7"/>
+    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="V11:Z11"/>
+    <mergeCell ref="BQ11:BR11"/>
+    <mergeCell ref="S10:U10"/>
     <mergeCell ref="E4:CX4"/>
     <mergeCell ref="E13:E17"/>
     <mergeCell ref="K7:O7"/>
@@ -32917,28 +32947,6 @@
     <mergeCell ref="H13:BT14"/>
     <mergeCell ref="BQ12:BR12"/>
     <mergeCell ref="S9:W9"/>
-    <mergeCell ref="E2:CX2"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="V10:Z10"/>
-    <mergeCell ref="S7:W7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="AC8:BP8"/>
-    <mergeCell ref="E3:CX3"/>
-    <mergeCell ref="AC7:BP7"/>
-    <mergeCell ref="K8:O8"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="V11:Z11"/>
-    <mergeCell ref="BQ11:BR11"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="CO13:CX14"/>
-    <mergeCell ref="K11:O11"/>
-    <mergeCell ref="BU13:CN14"/>
-    <mergeCell ref="AC10:BP10"/>
-    <mergeCell ref="K9:O9"/>
-    <mergeCell ref="AB12:AD12"/>
   </mergeCells>
   <conditionalFormatting sqref="K18:CO87 CS18:CX87 H18:J117 CP19:CR87">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
